--- a/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
@@ -575,46 +575,46 @@
         <v>263</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.4021835673580085</v>
+        <v>-0.4011450231369977</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2677418105498575</v>
+        <v>0.2660496060164661</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.790163511759289</v>
+        <v>-2.781651840029618</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.279879559635781</v>
+        <v>-2.273350069897667</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.29675204435874</v>
+        <v>-1.293922521222321</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.379919427982536</v>
+        <v>-1.376664729884212</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8200107610127603</v>
+        <v>0.8155836586492455</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7332652825415948</v>
+        <v>0.729081025577571</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.08958384234794892</v>
+        <v>-0.09098149915934783</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.322413804280089</v>
+        <v>-1.320078796969113</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.908920683546285</v>
+        <v>-1.904836133479918</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.637460142170667</v>
+        <v>-2.630832146776655</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.678149879947398</v>
+        <v>-2.671355681812649</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.664885057534327</v>
+        <v>-1.661700706398165</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>201</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.249657225682832</v>
+        <v>-1.245462205459283</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.368996059226539</v>
+        <v>-1.365063117066626</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.266689684032961</v>
+        <v>-1.262530398818782</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1407089083374515</v>
+        <v>-0.1409813772125617</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6794967684840785</v>
+        <v>-0.6785095236490051</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1164038246087031</v>
+        <v>0.114733454804977</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.03203338855887239</v>
+        <v>0.02985430440683956</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.554959286641299</v>
+        <v>2.543741398799959</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.49734866015735</v>
+        <v>1.490110038401347</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.139531887250648</v>
+        <v>3.126241901259853</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.434214951643781</v>
+        <v>3.419752828082316</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.471552512922109</v>
+        <v>2.460793252029042</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.553230366110121</v>
+        <v>0.5493587845949861</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3053061616295452</v>
+        <v>0.3018654930231577</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>87</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.217576251244196</v>
+        <v>-4.20219137917686</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.130228834173835</v>
+        <v>-8.101259695890064</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-11.97786100306619</v>
+        <v>-11.93420703245026</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.549911352708321</v>
+        <v>-9.51580779212906</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.54353698361591</v>
+        <v>-13.4954415134403</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-13.24939526363292</v>
+        <v>-13.20233832138806</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-14.48886921966427</v>
+        <v>-14.4381393730872</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-17.26397345245235</v>
+        <v>-17.20364595955394</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12.72196229672193</v>
+        <v>-12.67780431572918</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-11.27259296850369</v>
+        <v>-11.23427156327971</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.48073343931949</v>
+        <v>-11.44184088417035</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.60264687381282</v>
+        <v>-12.55916937292562</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-13.02808081996965</v>
+        <v>-12.98261549767656</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.47322567676442</v>
+        <v>-10.43754092317173</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>68</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-9.846379496680562</v>
+        <v>-9.809332039360172</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.106185671919292</v>
+        <v>-4.090927068232546</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.559744920147459</v>
+        <v>-1.552980038875766</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.42968668079191</v>
+        <v>-1.424332222518899</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.920051512800839</v>
+        <v>3.905196337168135</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.691759646638104</v>
+        <v>5.670312807980814</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.02826157626425</v>
+        <v>9.989868838514901</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.03681543307858</v>
+        <v>10.99434490587529</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.45289382379048</v>
+        <v>12.40518579488801</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.55351563588414</v>
+        <v>14.49728440520011</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>14.35264977717191</v>
+        <v>14.29698796426925</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.91568082603135</v>
+        <v>12.86598193716479</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.070362022746401</v>
+        <v>8.03921248494833</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.80020804496273</v>
+        <v>9.761918170810361</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.737330910559258</v>
+        <v>7.268572370631809</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10.92708530712493</v>
+        <v>11.8215297797446</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.958436143847</v>
+        <v>11.83708866744739</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.193555364484304</v>
+        <v>9.947907311932816</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.315478611509988</v>
+        <v>9.012199192905634</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.252309799326973</v>
+        <v>8.94641086283972</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.576430805590931</v>
+        <v>9.321843451257429</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>9.667390192910709</v>
+        <v>10.51146334100252</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12.69022558225642</v>
+        <v>13.78464166518243</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14.95179120139525</v>
+        <v>16.25149235235138</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>16.72068368659123</v>
+        <v>18.16979590209704</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>18.73117650253106</v>
+        <v>20.32989515517559</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>24.94246066549992</v>
+        <v>27.03394259092027</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>23.27923189709344</v>
+        <v>25.25211424924225</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4934383202099752</v>
+        <v>-0.4983880277777217</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8742427024050059</v>
+        <v>-0.8791010649037432</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8847347448446357</v>
+        <v>0.894116822486815</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.630372492836685</v>
+        <v>1.648539917250069</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.322720508533735</v>
+        <v>2.348747877337601</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.466316292403249</v>
+        <v>4.512595802053802</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9969671905155835</v>
+        <v>1.013932616264704</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.234969282442371</v>
+        <v>2.264896692717102</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.263319524878838</v>
+        <v>3.304078579266992</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.046057551201422</v>
+        <v>1.069208171073377</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.072898861757096</v>
+        <v>2.106690871600378</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.646568961668173</v>
+        <v>3.693869060001774</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.845550851926951</v>
+        <v>3.894732461479165</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.322189529153405</v>
+        <v>5.386689818600246</v>
       </c>
     </row>
     <row r="12">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.7865</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4094</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.09509402997378658</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.8739</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3831~3844</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3831</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.07408348150030264</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.9613</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3630~3643</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3630</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.009222014967036785</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 1.049</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3543~3556</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3543</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.09373828271466067</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 1.136</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3475~3488</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3475</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.2875249825423154</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 1.223</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3355~3358</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3355</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.03783029205923327</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 1.311</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3033~3033</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3033</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.09475818490047772</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 1.398</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2794~2794</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2794</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.369840133619654</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 1.486</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2536~2536</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2536</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.5428392823136861</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 1.573</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2362~2362</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2362</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.3854778525249927</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 1.66</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2102~2102</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2102</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.7891496912077258</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 1.748</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1898~1898</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1898</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.8258451360597832</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 1.835</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1688~1688</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1688</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7056138124914426</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 1.922</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1457~1457</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1457</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.7666852213137005</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 2.01</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1272~1272</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1272</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.8870648244441171</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 2.097</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1118~1118</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1118</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.7265974579653403</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 2.185</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>965~965</t>
-        </is>
+      <c r="B22" t="n">
+        <v>965</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.392572042484325</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 2.272</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>777~777</t>
-        </is>
+      <c r="B23" t="n">
+        <v>777</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.9171150903434295</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 2.359</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>637~637</t>
-        </is>
+      <c r="B24" t="n">
+        <v>637</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.137644882301799</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 2.447</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>548~548</t>
-        </is>
+      <c r="B25" t="n">
+        <v>548</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.163495986359365</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 2.534</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>469~469</t>
-        </is>
+      <c r="B26" t="n">
+        <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.730442276804951</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 2.622</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>403~403</t>
-        </is>
+      <c r="B27" t="n">
+        <v>403</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.593410315025757</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 2.709</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>347~347</t>
-        </is>
+      <c r="B28" t="n">
+        <v>347</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.837973783536427</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 2.796</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>301~301</t>
-        </is>
+      <c r="B29" t="n">
+        <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.323837427298336</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 2.884</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>249~249</t>
-        </is>
+      <c r="B30" t="n">
+        <v>249</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.125035575372358</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 2.971</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>208~208</t>
-        </is>
+      <c r="B31" t="n">
+        <v>208</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.795023218251565</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 3.058</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>175~175</t>
-        </is>
+      <c r="B32" t="n">
+        <v>175</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.6494188226471707</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 3.146</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B33" t="n">
+        <v>141</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.0111688166638757</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 3.233</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>114~114</t>
-        </is>
+      <c r="B34" t="n">
+        <v>114</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.769719574526874</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 3.321</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>4.649418822647164</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.7865</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.8739</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>347~347</t>
-        </is>
+      <c r="B7" t="n">
+        <v>347</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.8206827172540017</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.9613</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>548~548</t>
-        </is>
+      <c r="B8" t="n">
+        <v>548</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.06130620533747333</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 1.049</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>635~635</t>
-        </is>
+      <c r="B9" t="n">
+        <v>635</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.5249343832021083</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 1.136</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>703~703</t>
-        </is>
+      <c r="B10" t="n">
+        <v>703</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.426581990195757</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 1.223</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>823~833</t>
-        </is>
+      <c r="B11" t="n">
+        <v>823</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1525019456601555</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 1.311</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1145~1158</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1145</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.2481878884310404</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 1.398</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1384~1397</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1384</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.7396802672393221</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 1.486</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1642~1655</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1642</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.8318069002703936</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 1.573</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1816~1829</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1816</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4978122950596173</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 1.66</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2076~2089</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2076</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7940606275340585</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 1.748</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2280~2293</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2280</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.6835822364768802</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 1.835</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2490~2503</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2490</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4758594148963553</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 1.922</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2721~2734</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2721</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.4085809683445731</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 2.01</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2906~2919</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2906</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.3865524003744198</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 2.097</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3060~3073</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3060</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.2643462277921458</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 2.185</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3213~3226</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3213</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.4165629327332212</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 2.272</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3401~3414</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3401</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.2087283026352864</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 2.359</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3541~3554</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3541</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.3831400647232002</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 2.447</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3630~3643</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3630</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.4758703816977672</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 2.534</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3709~3722</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3709</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.3440562675501084</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 2.622</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3775~3788</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3775</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2759092811392208</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 2.709</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3831~3844</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3831</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2561854586074759</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 2.796</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3877~3890</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3877</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1798136415467368</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 2.884</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3929~3942</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3929</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1342297966178947</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 2.971</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3970~3983</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3970</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1459615439107012</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 3.058</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4003~4016</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4003</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.02829887797889796</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 3.146</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4037~4050</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4037</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.0003888402838470029</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 3.233</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4064~4077</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4064</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.07744616911848823</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 3.321</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4094~4107</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4094</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.09509402997378658</v>

--- a/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MVRV is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MVRV is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.8302</t>
+          <t>X ≈ 0.8303</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>263</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.4011450231369977</v>
+        <v>-0.3886661290633882</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2660496060164661</v>
+        <v>0.2789188733224677</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.781651840029618</v>
+        <v>-2.768684384766978</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.273350069897667</v>
+        <v>-2.260406486957635</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.293922521222321</v>
+        <v>-1.280843313393085</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.376664729884212</v>
+        <v>-1.36364987217447</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8155836586492455</v>
+        <v>0.8286264385086497</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.729081025577571</v>
+        <v>0.742241702042584</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.09098149915934783</v>
+        <v>-0.0778000119520712</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.320078796969113</v>
+        <v>-1.306687960531775</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.904836133479918</v>
+        <v>-1.891389694715713</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.630832146776655</v>
+        <v>-2.617387198980779</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.671355681812649</v>
+        <v>-2.657803338386771</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.661700706398165</v>
+        <v>-1.672130342096139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.9176</t>
+          <t>X ≈ 0.9177</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>201</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.245462205459283</v>
+        <v>-1.232989703272267</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.365063117066626</v>
+        <v>-1.352200438850922</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.262530398818782</v>
+        <v>-1.249566987198484</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1409813772125617</v>
+        <v>-0.1280408888381217</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6785095236490051</v>
+        <v>-0.6654339931203097</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.114733454804977</v>
+        <v>0.1277455702533032</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.02985430440683956</v>
+        <v>0.04289375754515845</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.543741398799959</v>
+        <v>2.556900373823616</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.490110038401347</v>
+        <v>1.503289941920947</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.126241901259853</v>
+        <v>3.139632236064962</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.419752828082316</v>
+        <v>3.433199058620822</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.460793252029042</v>
+        <v>2.474237998551445</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.5493587845949861</v>
+        <v>0.5629108808538632</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.3018654930231577</v>
+        <v>0.2914358573251121</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>87</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.20219137917686</v>
+        <v>-4.189726054006769</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.101259695890064</v>
+        <v>-8.088407333807496</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-11.93420703245026</v>
+        <v>-11.92125656313146</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.51580779212906</v>
+        <v>-9.502877876477356</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.4954415134403</v>
+        <v>-13.48237802126121</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-13.20233832138806</v>
+        <v>-13.18933714369955</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-14.4381393730872</v>
+        <v>-14.42511011655814</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-17.20364595955394</v>
+        <v>-17.19049807377427</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12.67780431572918</v>
+        <v>-12.6646315106949</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-11.23427156327971</v>
+        <v>-11.22088690512861</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.44184088417035</v>
+        <v>-11.428399023187</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.55916937292562</v>
+        <v>-12.54572759207398</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-12.98261549767656</v>
+        <v>-12.96906479289135</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.43754092317173</v>
+        <v>-10.44797055887014</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>68</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-9.809332039360172</v>
+        <v>-9.796875453680997</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.090927068232546</v>
+        <v>-4.078073630599654</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.552980038875766</v>
+        <v>-1.540023136743997</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.424332222518899</v>
+        <v>-1.411398151805251</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.905196337168135</v>
+        <v>3.918270230446261</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.670312807980814</v>
+        <v>5.68332422958062</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.989868838514901</v>
+        <v>10.00291022666346</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.99434490587529</v>
+        <v>11.00750494303356</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.40518579488801</v>
+        <v>12.41836759541678</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.49728440520011</v>
+        <v>14.51067651172663</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>14.29698796426925</v>
+        <v>14.31043540966388</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.86598193716479</v>
+        <v>12.87942737129685</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.03921248494833</v>
+        <v>8.052764646594611</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.761918170810361</v>
+        <v>9.751488535112209</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.268572370631809</v>
+        <v>6.788819048461569</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.8215297797446</v>
+        <v>11.29113241620334</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.83708866744739</v>
+        <v>11.3032848209611</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.947907311932816</v>
+        <v>9.430626381055333</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.012199192905634</v>
+        <v>8.498212324280018</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.94641086283972</v>
+        <v>8.43522217666046</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.321843451257429</v>
+        <v>8.806742670568759</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10.51146334100252</v>
+        <v>10.4300736195343</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13.78464166518243</v>
+        <v>13.67511394191159</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>16.25149235235138</v>
+        <v>16.11908717515692</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>18.16979590209704</v>
+        <v>17.56837368185137</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>20.32989515517559</v>
+        <v>19.71076924603896</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>27.03394259092027</v>
+        <v>26.35591145591931</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>25.25211424924225</v>
+        <v>25.39319976505924</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4983880277777217</v>
+        <v>-0.6468411260043609</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8791010649037432</v>
+        <v>-1.03097735708711</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.894116822486815</v>
+        <v>0.7356255097488216</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.648539917250069</v>
+        <v>1.488088200749417</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.348747877337601</v>
+        <v>2.184593057565252</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.512595802053802</v>
+        <v>4.342594727491829</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.013932616264704</v>
+        <v>1.164121864007662</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.264896692717102</v>
+        <v>1.932677403124984</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.304078579266992</v>
+        <v>2.968647590122735</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.069208171073377</v>
+        <v>0.7366026154239833</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.106690871600378</v>
+        <v>1.939389362933802</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.693869060001774</v>
+        <v>3.521755131388275</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.894732461479165</v>
+        <v>3.720799324514424</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.386689818600246</v>
+        <v>5.184925067620348</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.121053382971382</v>
+        <v>-2.901084097761149</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5485265775256991</v>
+        <v>-0.3105895185560641</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.198625409645388</v>
+        <v>-1.96586510499197</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.068372277037803</v>
+        <v>-1.835639961403508</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.443613575791979</v>
+        <v>-3.214265648952981</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.890941512553212</v>
+        <v>-1.656387417637042</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1163749793793443</v>
+        <v>-0.06042550799583779</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.06760162243894285</v>
+        <v>0.312841982671209</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8434218199386478</v>
+        <v>1.092195960602311</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4117066767515354</v>
+        <v>0.6624452314991558</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2069533524341409</v>
+        <v>0.4577440732390485</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2413365097795719</v>
+        <v>0.4921222255943718</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1789181011652303</v>
+        <v>0.07197137228106243</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7660168525711413</v>
+        <v>-0.5426291119464679</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>258</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.330647622535643</v>
+        <v>-1.318125332860021</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-6.042996429298178</v>
+        <v>-6.030086619722127</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.825462035119571</v>
+        <v>-6.812454903701969</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.857999600186581</v>
+        <v>-7.845020457788117</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.784017714483554</v>
+        <v>-8.770906910108614</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.323785079093476</v>
+        <v>-7.31074218279911</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.346503292489608</v>
+        <v>-9.333437038189132</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.9764773889457</v>
+        <v>-10.96329637965047</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-11.037477275128</v>
+        <v>-11.02427853617324</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.399230367132589</v>
+        <v>-8.385825239479757</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.7047588852487</v>
+        <v>-11.69130159153848</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-12.44556952635288</v>
+        <v>-12.43211723763277</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-12.86582413729779</v>
+        <v>-12.85226809094618</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-13.39129660347103</v>
+        <v>-13.40172623916918</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>174</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.67897547289347</v>
+        <v>2.691497762569092</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.366252434641737</v>
+        <v>3.379162244217788</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.82195844068881</v>
+        <v>1.834965572106412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2280736422619682</v>
+        <v>0.2410527846604325</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.563215645580478</v>
+        <v>2.576326449955417</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5876182787728368</v>
+        <v>-0.5745753824784714</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.396489927079728</v>
+        <v>-2.383423672779251</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5648227511484478</v>
+        <v>-0.55164174185321</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.349960568365105</v>
+        <v>-2.336761829410342</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.924223684427652</v>
+        <v>-4.910818556774821</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.85311493977958</v>
+        <v>-6.839657646069362</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.968157069790472</v>
+        <v>-7.954704781070362</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.664273749701024</v>
+        <v>-6.650717703349422</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.265127130068279</v>
+        <v>-5.275556765766432</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>260</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.878053704825447</v>
+        <v>-2.865531415149825</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2588580870203003</v>
+        <v>-0.2459482774442492</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.03834217823227</v>
+        <v>-1.025335046814668</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2457571082212127</v>
+        <v>0.2587362506196769</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.600356414543093</v>
+        <v>-2.587245610168154</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.995222169135126</v>
+        <v>-4.98217927284076</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.541494347945871</v>
+        <v>-3.528428093645395</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.777908515958138</v>
+        <v>-4.764727506662901</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.838908402140525</v>
+        <v>-4.825709663185762</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.535187433322129</v>
+        <v>-4.521782305669298</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.432248449947487</v>
+        <v>-2.418791156237269</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.167096061832908</v>
+        <v>-3.153643773112798</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.202735288162337</v>
+        <v>-3.189179241810734</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.029937032809215</v>
+        <v>-1.040366668507367</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>204</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4477381503783704</v>
+        <v>0.4602604400539931</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6736393841547397</v>
+        <v>-0.6607295745786885</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8922762229741679</v>
+        <v>0.90528335439177</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.00292151244463</v>
+        <v>2.015900654843094</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9743042189409792</v>
+        <v>0.9874150233159185</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.271746156656533</v>
+        <v>1.284789052950899</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6968163609531004</v>
+        <v>0.7098826152535764</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.170809432759839</v>
+        <v>3.183990442055077</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.129417389714675</v>
+        <v>2.142616128669438</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.710664753706126</v>
+        <v>4.724069881358957</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.525519272525919</v>
+        <v>3.538976566236137</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.172811708415423</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.428584837477366</v>
+        <v>1.418155201779214</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>210</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.792275965504309</v>
+        <v>1.804798255179932</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.60927378111154</v>
+        <v>1.622183590687591</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7382145983245181</v>
+        <v>0.7512217297421202</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.512484650020461</v>
+        <v>-1.499505507621997</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1461439603307255</v>
+        <v>-0.1330331559557862</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.75346392737697</v>
+        <v>-1.740421031082604</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.362007168458888</v>
+        <v>-1.348940914158412</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.733952472002287</v>
+        <v>-3.720771462707049</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.366380929613051</v>
+        <v>-2.353182190658288</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.645077543212253</v>
+        <v>-4.631672415559422</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.802211819910944</v>
+        <v>-5.788754526200727</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.672590567327418</v>
+        <v>-7.659138278607308</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.616654702081846</v>
+        <v>-7.603098655730243</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.890742893615133</v>
+        <v>-6.901172529313286</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>231</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3204144936428364</v>
+        <v>0.3329367833184591</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4404426122802079</v>
+        <v>0.453352421856259</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.77717563728546</v>
+        <v>1.790182768703062</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.421575559111382</v>
+        <v>-2.408596416712918</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.399310585123814</v>
+        <v>4.412421389498753</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.233549059636012</v>
+        <v>1.246591955930377</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.581715775264172</v>
+        <v>1.594782029564648</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.846134108084399</v>
+        <v>2.859315117379637</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>5.38253681930464</v>
+        <v>5.395735558259403</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.398212500077541</v>
+        <v>5.411617627730372</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.894757877058758</v>
+        <v>3.908215170768976</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7.837890752463615</v>
+        <v>7.851446798815218</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.758607755735618</v>
+        <v>3.748178120037466</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>185</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.06100588777754723</v>
+        <v>-0.04848359810192449</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05095787912011929</v>
+        <v>-0.03804806954406814</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.797416657526476</v>
+        <v>2.810423788944078</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.468210330674516</v>
+        <v>3.48118947307298</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.308167493980726</v>
+        <v>1.321278298355665</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.065068891155839</v>
+        <v>1.078111787450204</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.262908069359682</v>
+        <v>-2.249841815059206</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.811172549222263</v>
+        <v>-3.797991539927025</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.574875138107203</v>
+        <v>-6.561676399152439</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.343919242054106</v>
+        <v>-6.330514114401275</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.008132025831152</v>
+        <v>-5.994674732120934</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.595370490107335</v>
+        <v>-7.581918201387225</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.25886834429548</v>
+        <v>-11.24531229794388</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-12.63076863364076</v>
+        <v>-12.64119826933891</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>154</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.806310634472936</v>
+        <v>-2.793400824896885</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.201179341069526</v>
+        <v>-3.188172209651924</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-10.21378335131917</v>
+        <v>-10.2008042089207</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-10.10285391704076</v>
+        <v>-10.08974311266582</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.1560613299743</v>
+        <v>-9.143018433679934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.591444397896005</v>
+        <v>-8.578378143595529</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-9.707978446028157</v>
+        <v>-9.694797436732919</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.470277033509163</v>
+        <v>-8.4570782945544</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.372350270484986</v>
+        <v>-7.358945142832155</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.69856459330137</v>
+        <v>-1.68511230458126</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.118819204246272</v>
+        <v>-2.105263157894669</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.0789540760817502</v>
+        <v>0.06852444038359806</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>153</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.473830477072724</v>
+        <v>-3.461308187397101</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.817430233827821</v>
+        <v>-1.80452042425177</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.055674915784657</v>
+        <v>1.068682047202259</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7748562653332556</v>
+        <v>-0.7618771229347914</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.954696375803799</v>
+        <v>1.967807180178738</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.559327856002973</v>
+        <v>3.572370752297338</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.474594138730836</v>
+        <v>3.487660393031312</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.35381596870743</v>
+        <v>2.366996978002668</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.171688187470188</v>
+        <v>-1.158283059817357</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.030036283029595</v>
+        <v>-2.016578989319378</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6187259592831609</v>
+        <v>0.6321782480032709</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.81285043330557</v>
+        <v>2.826406479657173</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.512591633110802</v>
+        <v>-1.523021268808954</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>188</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.357625509577289</v>
+        <v>3.370147799252912</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.214137002995983</v>
+        <v>1.227046812572034</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.010757658101575</v>
+        <v>4.023764789519177</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.20484057794306</v>
+        <v>5.217819720341524</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.474930001168758</v>
+        <v>1.488040805543697</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.240457045267377</v>
+        <v>1.253499941561742</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.68763822161209</v>
+        <v>1.700704475912566</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.284284610064695</v>
+        <v>2.297465619359933</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.691369830265401</v>
+        <v>1.704568569220164</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.905074432471508</v>
+        <v>1.918479560124339</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.764150895388006</v>
+        <v>2.777608189098224</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.862363839967415</v>
+        <v>3.875816128687525</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.378279441788479</v>
+        <v>2.391835488140082</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.223745454915829</v>
+        <v>4.213315819217677</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>140</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.636295463067164</v>
+        <v>-4.623773173391541</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.81929764745994</v>
+        <v>-4.806387837883889</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.071309211199399</v>
+        <v>-3.058302079781797</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.226770364306176</v>
+        <v>-2.213791221907712</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.520522706335981</v>
+        <v>1.533633510710921</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.46774964166265</v>
+        <v>-2.454706745368284</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.591095329145041</v>
+        <v>-1.577914319849803</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.509238072470232</v>
+        <v>-4.496039333515469</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.502220400355313</v>
+        <v>-2.488815272702482</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.421259438958558</v>
+        <v>-8.40780214524834</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.672590567327418</v>
+        <v>-7.659138278607308</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.94998803541521</v>
+        <v>-5.936431989063607</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>89</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.178831578636938</v>
+        <v>-4.166309288961315</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.914000697219237</v>
+        <v>-6.901090887643186</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.308869403815699</v>
+        <v>-7.295862272398097</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.931425259972315</v>
+        <v>-4.918446117573851</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-12.21141950875235</v>
+        <v>-12.19830870437741</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-8.543191054182749</v>
+        <v>-8.530148157888384</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.99871128830897</v>
+        <v>-11.98564503400849</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-13.58949019270838</v>
+        <v>-13.57630918341314</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.89768109012677</v>
+        <v>-15.884482351172</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-18.99499728639058</v>
+        <v>-18.98159215873775</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-13.58177308261828</v>
+        <v>-13.56831578890806</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-13.54738992527285</v>
+        <v>-13.53393763655274</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-10.59685801936375</v>
+        <v>-10.58330197301215</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.852754664615681</v>
+        <v>-5.863184300313833</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>79</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.734409781055845</v>
+        <v>5.746932070731468</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.122836168091737</v>
+        <v>4.135745977667789</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.398614816986012</v>
+        <v>-6.385607685568409</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.534184469188709</v>
+        <v>-7.521205326790245</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.806782899450752</v>
+        <v>-6.793672095075813</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.775163746545218</v>
+        <v>-7.762120850250852</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.062429109387047</v>
+        <v>-4.049362855086571</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.327080862598997</v>
+        <v>-8.313899853303759</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7.12225796397103</v>
+        <v>-7.109059225016267</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.440737579378776</v>
+        <v>-5.427332451725945</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5821997644558508</v>
+        <v>-0.568742470745633</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.7180061776997135</v>
+        <v>0.7314584664198236</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.499716787675645</v>
+        <v>-3.486160741324042</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.984172670589089</v>
+        <v>-1.994602306287241</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 2.578</t>
+          <t>X ≈ 2.577</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>66</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.56716774039608</v>
+        <v>3.579690030071703</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.501048672886284</v>
+        <v>6.513958482462336</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.106179966289744</v>
+        <v>6.119187097707346</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>12.29703915950343</v>
+        <v>12.3100183019019</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.24346642927961</v>
+        <v>10.25657723365455</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>13.57121139729844</v>
+        <v>13.58425429359281</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.941023134571523</v>
+        <v>8.954089388871999</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>17.56474882669912</v>
+        <v>17.57792983599436</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>17.50374894051682</v>
+        <v>17.51694767947158</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>16.65362375548889</v>
+        <v>16.66702888314173</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>19.47917346147433</v>
+        <v>19.49263075518455</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>17.99840510366826</v>
+        <v>18.01185739238837</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.5478474624204</v>
+        <v>14.561403508772</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>13.2824172795451</v>
+        <v>13.27198764384695</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>56</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5335833617456629</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.499880639770872</v>
+        <v>-4.48687350835327</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.798198935734753</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.234808420621704</v>
+        <v>2.247919224996643</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>7.350657108721627</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.919333356101284</v>
+        <v>1.932532095056047</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.684552289815443</v>
+        <v>2.698004578535553</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.050011964584819</v>
+        <v>4.063568010936422</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.514019011146871</v>
+        <v>2.503589375448719</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>46</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.202213853703071</v>
+        <v>6.214736143378694</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.938466327695338</v>
+        <v>8.951376137271389</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.71751066457701</v>
+        <v>10.73051779599461</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.84776379718451</v>
+        <v>10.86074293958297</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>3.800714256052494</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.085045389393215</v>
+        <v>4.098088285687581</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.34813775907746</v>
+        <v>8.361204013377936</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.880954360295959</v>
+        <v>7.894135369591197</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.472128387157071</v>
+        <v>3.485327126111834</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.930576209144903</v>
+        <v>-1.917118915434685</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>0.2911722803989036</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.553117554646938</v>
+        <v>8.566673600998541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1071867130101225</v>
+        <v>0.09675707731197036</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>52</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.275792449020742</v>
+        <v>3.288314738696364</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.028088856251095</v>
+        <v>-6.015179046675044</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.422957562847742</v>
+        <v>-6.40995043143014</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.322680185144421</v>
+        <v>3.335659327542885</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>12.39964358545681</v>
+        <v>12.41275438983175</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.69708552317248</v>
+        <v>12.71012841946684</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.53542872897712</v>
+        <v>14.54849498327759</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.299014560964849</v>
+        <v>8.312195570260087</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>14.00724544401331</v>
+        <v>14.02044418296808</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.310966412831547</v>
+        <v>9.324371540484378</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>12.95236693466781</v>
+        <v>12.96582422837803</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.140596245859399</v>
+        <v>9.154048534579509</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.797264711837627</v>
+        <v>6.81082075818923</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.970062967190785</v>
+        <v>8.959633331492633</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>41</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.273926125087954</v>
+        <v>-1.261403835412331</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.992549042435449</v>
+        <v>2.0054588520115</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.47572911632674</v>
+        <v>6.488736247744342</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.48403102942196</v>
+        <v>11.49701017182043</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.249512136869633</v>
+        <v>-1.236401332494694</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.486954191089964</v>
+        <v>1.49999708738433</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.036803916426223</v>
+        <v>-1.023737662125747</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.503987315207752</v>
+        <v>-1.490806305912514</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.313061579097742</v>
+        <v>3.326260318052505</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.02391200382592018</v>
+        <v>0.03731713147875126</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.61986571073556</v>
+        <v>-2.606408417025342</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.585482553390129</v>
+        <v>-2.572030264670019</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.005737164335109</v>
+        <v>-2.992181117983506</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.07308900279042</v>
+        <v>-10.08351863848857</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>33</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.136482996592811</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.266736129200311</v>
+        <v>9.279715271598775</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.05605988214676</v>
+        <v>12.06910277844112</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.0622352557836</v>
+        <v>21.07530151008407</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>17.56474882669912</v>
+        <v>17.57792983599436</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14.47344591021379</v>
+        <v>14.48664464916855</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.41856740086828</v>
+        <v>13.4320246945785</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.45295055821371</v>
+        <v>13.46640284693382</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.03269594726881</v>
+        <v>13.04625199362042</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.28241727954506</v>
+        <v>13.27198764384691</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.388914620966496</v>
+        <v>3.401436910642119</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>13.1471781837586</v>
+        <v>13.1601853151762</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.33625484577785</v>
+        <v>10.34923398817632</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.9743042189409792</v>
+        <v>0.9874150233159185</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.212922627244922</v>
+        <v>4.225965523539287</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.01054185114911</v>
+        <v>10.02360810544958</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.543358452367563</v>
+        <v>9.556539461662801</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>24.18824091912648</v>
+        <v>24.20143965808124</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.33811573409851</v>
+        <v>23.35152086175134</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.1921859391927</v>
+        <v>20.20564323290291</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.2853926259499</v>
+        <v>17.29884491467001</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>19.80631448559327</v>
+        <v>19.81987053194487</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.11485934728128</v>
+        <v>17.10442971158313</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>27</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-11.75269757946926</v>
+        <v>-11.74017528979363</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>16.00074286320702</v>
+        <v>16.01372200560548</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>19.16602535183858</v>
+        <v>19.17913615621352</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>19.46346728955425</v>
+        <v>19.47651018584861</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>15.6750298685782</v>
+        <v>15.68809612287868</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>26.31895758090787</v>
+        <v>26.33213859020311</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>15.1468465836144</v>
+        <v>15.16004532256916</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.09196807426895</v>
+        <v>14.10542536797917</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.718943824206974</v>
+        <v>6.732396112927084</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.298689213262023</v>
+        <v>6.312245259613626</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 3.277</t>
+          <t>X ≈ 3.276</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>30</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209954</v>
+        <v>-2.480916030534331</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.438345266507568</v>
+        <v>-7.425435456931517</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.833213973104158</v>
+        <v>-7.820206841686556</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-14.3696275071633</v>
+        <v>-14.35664836476484</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.758617944431194</v>
+        <v>1.771728748806133</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.38939321548019</v>
+        <v>5.402436111774556</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.971326164874576</v>
+        <v>1.984392419175052</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.25968436154951</v>
+        <v>7.273089489202341</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.05493103723191</v>
+        <v>7.068388330942128</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.66905958363246</v>
+        <v>6.682615629984063</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.585447582575419</v>
+        <v>3.575017946877267</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MVRV is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MVRV is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,105 +2210,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.7865</t>
+          <t>X &gt; 0.7866</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09509402997378658</v>
+        <v>-0.09532693608449705</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2326300529988785</v>
+        <v>-0.2328374535226985</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2733276556051649</v>
+        <v>-0.2735271858982742</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3491596709060119</v>
+        <v>-0.3493402039853279</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4600838185065186</v>
+        <v>-0.46024006211006</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4175302364944784</v>
+        <v>-0.4176954992418018</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4890493532917475</v>
+        <v>-0.4891976994662812</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5039873152077519</v>
+        <v>-0.5041344055431836</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5028602102738446</v>
+        <v>-0.5030079746304139</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.6319701040434751</v>
+        <v>-0.6320906360314709</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.7011506485544317</v>
+        <v>-0.7012553977059923</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6776128887559878</v>
+        <v>-0.6777233059792493</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6691577545848943</v>
+        <v>-0.6692723908492866</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.723296921577024</v>
+        <v>-0.722906351047051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.8739</t>
+          <t>X &gt; 0.874</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07408348150030264</v>
+        <v>-0.07519431401939869</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2668646524040028</v>
+        <v>-0.267960604347401</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1011299890680704</v>
+        <v>-0.1022781401512916</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2170630708186252</v>
+        <v>-0.2181788176539783</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4028403889021561</v>
+        <v>-0.4039199537887015</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3516851903546865</v>
+        <v>-0.3527722215587943</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.578613039572204</v>
+        <v>-0.5796433540297983</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.5886380522546091</v>
+        <v>-0.5896763983132871</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5311358826891706</v>
+        <v>-0.5321910889791539</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5847311099846237</v>
+        <v>-0.5857912893864849</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6185170587513937</v>
+        <v>-0.6195734248162381</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.5435234434781364</v>
+        <v>-0.5445991922372357</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.5317059000140461</v>
+        <v>-0.5327944056712255</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6588750485913977</v>
+        <v>-0.6577586710768273</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.009222014967036785</v>
+        <v>-0.01110263865729166</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2060553159309535</v>
+        <v>-0.2079407181631012</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.0368210407595555</v>
+        <v>-0.03876807177990571</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2212758588116799</v>
+        <v>-0.2231685515267401</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3875760649120537</v>
+        <v>-0.3894434123660488</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3775116773180756</v>
+        <v>-0.3793720772884015</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6123050329991457</v>
+        <v>-0.6141049236873499</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7620838565692054</v>
+        <v>-0.7638603507229647</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6430561113776463</v>
+        <v>-0.6448685021465792</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.7902147395328782</v>
+        <v>-0.7920182595367891</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.8421237384355749</v>
+        <v>-0.8439213370087018</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7098781695929972</v>
+        <v>-0.7117119092156159</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5915665065171964</v>
+        <v>-0.5934489808823287</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7120730785816249</v>
+        <v>-0.7103029013739288</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09373828271466067</v>
+        <v>0.09147643502651448</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.0121849289548166</v>
+        <v>-0.01448682551043845</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2553247625927142</v>
+        <v>0.2529295858802527</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.006955661989501039</v>
+        <v>0.004634696574477459</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.06570637989315031</v>
+        <v>-0.06803107856980972</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.06259214075750918</v>
+        <v>-0.0649062305678072</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2728052905245022</v>
+        <v>-0.2750650106569381</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3583537117880411</v>
+        <v>-0.3606104969121731</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3475373155044963</v>
+        <v>-0.3498009565078348</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5337561045721131</v>
+        <v>-0.5360048362392362</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5818427924353173</v>
+        <v>-0.584087940085027</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4189133559633262</v>
+        <v>-0.4212041878813366</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.287298580400666</v>
+        <v>-0.2896457710502744</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4732597276137085</v>
+        <v>-0.4712574481566136</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3475</v>
+        <v>3476</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2875249825423154</v>
+        <v>0.2849194524120477</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06762930571306214</v>
+        <v>0.06500796814493981</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2907102953984264</v>
+        <v>0.288004610373477</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.03496359757125589</v>
+        <v>0.0323361447015813</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1434103755075924</v>
+        <v>-0.146013958032718</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1747756045026065</v>
+        <v>-0.1773572292128378</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.4736288418265744</v>
+        <v>-0.4761301188668909</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5805072386948353</v>
+        <v>-0.5830017080503467</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.5970870051467116</v>
+        <v>-0.59958100873191</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.827888695842482</v>
+        <v>-0.8303587866597439</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8729968906960153</v>
+        <v>-0.8754652668350076</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6788767746489981</v>
+        <v>-0.6814006625718179</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4502346242693633</v>
+        <v>-0.4528459748477047</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6735452231799925</v>
+        <v>-0.6712421221676266</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3355</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.03783029205923327</v>
+        <v>0.05035258173485602</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3527784608692883</v>
+        <v>-0.3398686512932372</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.122274922081715</v>
+        <v>-0.1092677906641129</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3195977275325887</v>
+        <v>-0.3066185851341245</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4708837430812309</v>
+        <v>-0.4577729387062917</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5010177434239367</v>
+        <v>-0.4879748471295713</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.8239885065568515</v>
+        <v>-0.8109222522563755</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9772394203829649</v>
+        <v>-0.9801945887173318</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.111485646112286</v>
+        <v>-1.114406072525604</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.438775648385928</v>
+        <v>-1.441650280364613</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.554110194760142</v>
+        <v>-1.540652901049924</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.430308259471339</v>
+        <v>-1.416855970751229</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.433275240013856</v>
+        <v>-1.419719193662253</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.600841538139953</v>
+        <v>-1.611271173838105</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.09475818490047772</v>
+        <v>0.1246248665632734</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2969011517696813</v>
+        <v>-0.2662446038092554</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2301806727414828</v>
+        <v>-0.199274563762188</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5285460696427151</v>
+        <v>-0.4978093146329314</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7702313796703706</v>
+        <v>-0.73926509464156</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.033290595927681</v>
+        <v>-1.002577080837597</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.019112344851791</v>
+        <v>-1.021324379417749</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.321442463053003</v>
+        <v>-1.290503841146446</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.580266285931643</v>
+        <v>-1.549375179727264</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.705037036406331</v>
+        <v>-1.673700308510952</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.94276101683996</v>
+        <v>-1.911382997114153</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.974319171726648</v>
+        <v>-1.942967905444846</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.99892590927886</v>
+        <v>-1.967340394642157</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.342676387091601</v>
+        <v>-2.335272290589778</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2794</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.369840133619654</v>
+        <v>0.3823624232952767</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2753770011770911</v>
+        <v>-0.2624671916010399</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.06179903633488237</v>
+        <v>-0.04879190491728025</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3968286524747029</v>
+        <v>-0.3838495100762387</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5415490801453018</v>
+        <v>-0.5284382757703625</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9599267558870537</v>
+        <v>-0.9468838595926883</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.116242434505061</v>
+        <v>-1.103176180204585</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.440261910595083</v>
+        <v>-1.427080901299846</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.787589642160349</v>
+        <v>-1.774390903205585</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.886104233057992</v>
+        <v>-1.872699105405161</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.12664853804845</v>
+        <v>-2.113191244338232</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.163847342048754</v>
+        <v>-2.150395053328644</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.154610184919214</v>
+        <v>-2.141054138567611</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.477544543408847</v>
+        <v>-2.487974179106999</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2536</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5428392823136861</v>
+        <v>0.5553615719893088</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3113918523147206</v>
+        <v>0.3243016618907717</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6263023255288616</v>
+        <v>0.6393094569464637</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3622336915748505</v>
+        <v>0.3752128339733147</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2969985963764969</v>
+        <v>0.3101094007514362</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3124995289993322</v>
+        <v>-0.2994566327049668</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2789367163031571</v>
+        <v>-0.2658704620026811</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4700948784915866</v>
+        <v>-0.4569138691963488</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.8465521779231082</v>
+        <v>-0.833353438968345</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.223491243077213</v>
+        <v>-1.210086115424382</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.152219330801735</v>
+        <v>-1.138762037091517</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.117836173456304</v>
+        <v>-1.104383884736194</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.06490466452739</v>
+        <v>-1.051348618175787</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.367233805437216</v>
+        <v>-1.377663441135368</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2362</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3854778525249927</v>
+        <v>0.3980001422006154</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.08635131830756393</v>
+        <v>0.09926112788361507</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5382226625153805</v>
+        <v>0.5512297939329827</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3721167773413327</v>
+        <v>0.385095919739797</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1300545800507109</v>
+        <v>0.1431653844256502</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2922325254173757</v>
+        <v>-0.2791896291230103</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.122944227448329</v>
+        <v>-0.109877973147853</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4631166186091704</v>
+        <v>-0.4499356093139326</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7358015174925754</v>
+        <v>-0.7226027785378122</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9508716644171926</v>
+        <v>-0.9374665367643615</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7322549633325792</v>
+        <v>-0.7187976696223615</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6131978009067112</v>
+        <v>-0.5997455121866011</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.652419388989621</v>
+        <v>-0.6388633426380181</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.080090097356866</v>
+        <v>-1.090519733055018</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2102</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7891496912077258</v>
+        <v>0.8016719808833486</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1290508641616341</v>
+        <v>0.1419606737376853</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7332306827791299</v>
+        <v>0.7462378141967321</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3877464224275471</v>
+        <v>0.4007255648260113</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4677838182021858</v>
+        <v>0.4808946225771251</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2894883629587568</v>
+        <v>0.3025312592531222</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2999021242782973</v>
+        <v>0.3129683785787734</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.0705874219763416</v>
+        <v>0.0837684312715794</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2282811606855049</v>
+        <v>-0.2150824217307417</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5075214741625302</v>
+        <v>-0.4941163465096992</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5219798412964778</v>
+        <v>-0.50852254758626</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2973017267674081</v>
+        <v>-0.283849438047298</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3369664233450393</v>
+        <v>-0.3234103769934364</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.08629361628283</v>
+        <v>-1.096723251980983</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1898</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8258451360597832</v>
+        <v>0.8383674257354059</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2153252638752932</v>
+        <v>0.2282350734513443</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7161362200816583</v>
+        <v>0.7291433514992605</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2141448848282508</v>
+        <v>0.227124027226715</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4133422155938007</v>
+        <v>0.42645301996874</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1839137634253731</v>
+        <v>0.1969566597197385</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2572411631183158</v>
+        <v>0.2703074174187918</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2626292746515944</v>
+        <v>-0.2494482653563566</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4816902777991174</v>
+        <v>-0.4684915388443542</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.06838026788499</v>
+        <v>-1.054975140232159</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.9570113582721262</v>
+        <v>-0.9435540645619085</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5538189280078356</v>
+        <v>-0.5403666392877255</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6052642660338705</v>
+        <v>-0.5917082196822676</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.35659667453735</v>
+        <v>-1.367026310235502</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1688</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7056138124914426</v>
+        <v>0.7181361021670654</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04190749810538108</v>
+        <v>0.05481730768143223</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7133895024092709</v>
+        <v>0.726396633826873</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.428950691888808</v>
+        <v>0.4419298342872722</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4829465384280169</v>
+        <v>0.4960573428029562</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4249382391768535</v>
+        <v>0.4379811354712189</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4586879342268446</v>
+        <v>0.4717541885273207</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1692296539287597</v>
+        <v>0.1824106632239975</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2472204692203661</v>
+        <v>-0.2340217302656029</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6234120049591994</v>
+        <v>-0.6100068773063683</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3542316799876772</v>
+        <v>-0.3407743862774595</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3318102451302707</v>
+        <v>0.3452625338503807</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2670058711521932</v>
+        <v>0.2805619175037961</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.668106919794262</v>
+        <v>-0.6785365554924141</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1457</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7666852213137005</v>
+        <v>0.7792075109893233</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.02127823379193217</v>
+        <v>-0.008368424215881021</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5447315771131827</v>
+        <v>0.5577387085307848</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.880887249185335</v>
+        <v>0.8938663915837992</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1379732246376904</v>
+        <v>-0.1248624202627511</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2967370727210792</v>
+        <v>0.3097799690154446</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2806375352703441</v>
+        <v>0.2937037895708201</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2551800433327003</v>
+        <v>-0.2419990340374625</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.139790087373612</v>
+        <v>-1.126591348418849</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.578110193472234</v>
+        <v>-1.564705065819403</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.027887539752761</v>
+        <v>-1.014430246042544</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5130651236564674</v>
+        <v>-0.4996128349363573</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9333197346013691</v>
+        <v>-0.9197636882497662</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.369940200540597</v>
+        <v>-1.380369836238749</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1272</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8870648244441171</v>
+        <v>0.8995871141197398</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.01696161870882662</v>
+        <v>-0.004051809132775475</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2171004923046453</v>
+        <v>0.2301076237222475</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5045863293146695</v>
+        <v>0.5175654717131337</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3483002945625344</v>
+        <v>-0.3351894901875951</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1849906997568951</v>
+        <v>0.1980335960512605</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6505714478934266</v>
+        <v>0.6636377021939026</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2620044013131775</v>
+        <v>0.2751854106084153</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.3493099502779202</v>
+        <v>-0.336111211323157</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8849697265008132</v>
+        <v>-0.8715645988479821</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3035595288058204</v>
+        <v>-0.2901022350956026</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5169871505521897</v>
+        <v>0.5304394392722998</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5684306528148326</v>
+        <v>0.5819866991664355</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2678375196823097</v>
+        <v>0.2574078839841576</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1118</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7265974579653403</v>
+        <v>0.739119747640963</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3672599809581456</v>
+        <v>0.3801697905341967</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6879547806227393</v>
+        <v>0.7009619120403414</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.980998610904656</v>
+        <v>1.99397775330312</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.9953502044192533</v>
+        <v>1.008461008794193</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.471683018700197</v>
+        <v>1.484725914994563</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.923621931123812</v>
+        <v>1.936688185424288</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.635329408907609</v>
+        <v>1.648510418202846</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7693205781814783</v>
+        <v>0.7825193171362415</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.008640831436188989</v>
+        <v>0.02204595908902007</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5194510133798005</v>
+        <v>0.5329083070900182</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8221704855731673</v>
+        <v>0.8356227742932774</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9385885043241515</v>
+        <v>0.9521445506757544</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2938554537739719</v>
+        <v>0.2834258180758198</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>965</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.392572042484325</v>
+        <v>1.405094332159948</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7136409165667033</v>
+        <v>0.7265507261427544</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6296530389856585</v>
+        <v>0.6426601704032606</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.417937259676059</v>
+        <v>2.430916402074523</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8432466145520721</v>
+        <v>0.8563574189270113</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.140688552267733</v>
+        <v>1.153731448562098</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.677716493026537</v>
+        <v>1.690782747327013</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.521413923260589</v>
+        <v>1.534594932555827</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8386523790471969</v>
+        <v>0.8518511180019601</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1957810800296329</v>
+        <v>0.209186207682464</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9236702427586891</v>
+        <v>0.9371275364689069</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8544264570989313</v>
+        <v>0.8678787458190413</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.641425732164393</v>
+        <v>0.6549817785159959</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5802662354251424</v>
+        <v>0.5698365997269903</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>777</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9171150903434295</v>
+        <v>0.9296373800190523</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.5925427643804611</v>
+        <v>0.6054525739565122</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1884263283165097</v>
+        <v>-0.1754191968989076</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.743628606092791</v>
+        <v>1.756607748491255</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6904068762201092</v>
+        <v>0.7035176805950485</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.116548942635902</v>
+        <v>1.129591838930267</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.67531586886426</v>
+        <v>1.688382123164736</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.336832598782891</v>
+        <v>1.350013608078129</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6323320690999381</v>
+        <v>0.6455308080547013</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2177931159279893</v>
+        <v>-0.2043879882751582</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4783544606553392</v>
+        <v>0.4918117543655569</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1266372319003821</v>
+        <v>0.1400895206204922</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2211831357560001</v>
+        <v>0.234739182107603</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3012963041684884</v>
+        <v>-0.3117259398666405</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>637</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.137644882301799</v>
+        <v>2.150167171977422</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.781958239510224</v>
+        <v>1.794868049086276</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4451743052841266</v>
+        <v>0.4581814367017287</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.616243764422229</v>
+        <v>2.629222906820694</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5079638366342039</v>
+        <v>0.5210746410091431</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.904306873250974</v>
+        <v>1.917349769545339</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.290530769793442</v>
+        <v>2.303597024093918</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.76234748482964</v>
+        <v>1.775546223784403</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2842788147153783</v>
+        <v>0.2976839423682094</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.434313559471576</v>
+        <v>2.447770853181794</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.840753231730673</v>
+        <v>1.854205520450783</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.577484492057359</v>
+        <v>1.591040538408961</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.042276467975711</v>
+        <v>1.031846832277559</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>548</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.163495986359365</v>
+        <v>3.176018276034988</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.194258139818473</v>
+        <v>3.207167949394524</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.704498922272968</v>
+        <v>1.71750605369057</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.842051324953466</v>
+        <v>3.855030467351931</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.573703102582023</v>
+        <v>2.586813906956962</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.601072047596958</v>
+        <v>3.614114943891323</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.611228841273586</v>
+        <v>4.624295095574062</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.509008946141712</v>
+        <v>4.52218995543695</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.630490811784242</v>
+        <v>4.643689550739005</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.415402123106674</v>
+        <v>3.428807250759505</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.035466317037269</v>
+        <v>5.048923610747487</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.339922467083433</v>
+        <v>4.353374755803543</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.554704352488891</v>
+        <v>3.568260398840494</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.162089918341827</v>
+        <v>2.151660282643675</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.730442276804951</v>
+        <v>2.742964566480573</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.069415735495696</v>
+        <v>3.082422866913298</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.758304262559498</v>
+        <v>5.771283404957963</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.153784966463867</v>
+        <v>4.166895770838806</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.51732498520299</v>
+        <v>5.530367881497355</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.07225011654478</v>
+        <v>6.085316370845256</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.671164798786734</v>
+        <v>6.684345808081972</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.610164912604432</v>
+        <v>6.623363651559195</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.907161262757739</v>
+        <v>4.920566390410571</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.981725635668305</v>
+        <v>5.995182929378522</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.950010711990281</v>
+        <v>4.963463000710391</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.742975717250076</v>
+        <v>4.756531763601679</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.860500887479446</v>
+        <v>2.850071251781294</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 2.622</t>
+          <t>X &gt; 2.621</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>403</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.593410315025757</v>
+        <v>2.60593260470138</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.470670448959766</v>
+        <v>2.483580258535817</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.572079657995921</v>
+        <v>2.585086789413523</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.687444453134447</v>
+        <v>4.700423595532911</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.156467406796772</v>
+        <v>3.169578211171711</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.198326217961558</v>
+        <v>4.211369114255923</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.602426247587545</v>
+        <v>5.615492501888021</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.887103890989664</v>
+        <v>4.900284900284902</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.826104004807362</v>
+        <v>4.839302743762126</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.983422988513929</v>
+        <v>2.99682811616676</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.771225495461856</v>
+        <v>3.784682789172074</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.813052821541781</v>
+        <v>2.826505110261891</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.137215084046005</v>
+        <v>3.150771130397608</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.153685795974901</v>
+        <v>1.143256160276749</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>347</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.837973783536427</v>
+        <v>2.850496073212049</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.955506798814241</v>
+        <v>2.968416608390292</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.71337584437903</v>
+        <v>3.726382975796632</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.572735605228608</v>
+        <v>5.585714747627073</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.30520776191436</v>
+        <v>3.3183185662893</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.467203013751067</v>
+        <v>4.480245910045433</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.958838172559474</v>
+        <v>4.97190442685995</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.491654773777974</v>
+        <v>4.504835783073212</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.295208201716704</v>
+        <v>5.308406940671468</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.292345264527398</v>
+        <v>3.305750392180229</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.663960816290512</v>
+        <v>3.67741811000073</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.833790659514911</v>
+        <v>2.847242948235021</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.989904924650695</v>
+        <v>3.003460971002298</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.9341507526042108</v>
+        <v>0.9237211169060586</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.323837427298336</v>
+        <v>2.336359716973959</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.041167468819125</v>
+        <v>2.054077278395177</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.766585117421393</v>
+        <v>4.779564259819857</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.231486161485442</v>
+        <v>3.244596965860381</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.525605840064884</v>
+        <v>4.538648736359249</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.440872122792605</v>
+        <v>4.453938377093081</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.973688724011105</v>
+        <v>3.986869733306342</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.573818405935114</v>
+        <v>5.587017144889877</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.727015480043406</v>
+        <v>3.740420607696237</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.518939896589607</v>
+        <v>4.532397190299825</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.224419399449992</v>
+        <v>3.237871688170102</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.13971296126256</v>
+        <v>2.153269007614163</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.060530639053802</v>
+        <v>1.05010100335565</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>249</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.125035575372358</v>
+        <v>2.137557865047981</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.726313368030581</v>
+        <v>3.739223177606632</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.536263938542433</v>
+        <v>4.549271069960035</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.068123496852735</v>
+        <v>5.081102639251199</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.316850876158085</v>
+        <v>1.329961680533025</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.819112090982181</v>
+        <v>2.832154987276546</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.332771948007085</v>
+        <v>2.345838202307561</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.070407826334019</v>
+        <v>3.083588835629257</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.812620791557343</v>
+        <v>3.825819530512106</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.560889180826599</v>
+        <v>2.574294308479431</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.757742282211836</v>
+        <v>2.771199575922054</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.988912588151642</v>
+        <v>2.002364876871752</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.167051551503924</v>
+        <v>1.180607597855527</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.5912592447338412</v>
+        <v>-0.6016888804319933</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>208</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.795023218251565</v>
+        <v>2.807545507927188</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.068064989902695</v>
+        <v>4.080974799478746</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.153965514075331</v>
+        <v>4.166972645492933</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.803449415913605</v>
+        <v>3.816428558312069</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.822720508533735</v>
+        <v>1.835831312908674</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.081700907787855</v>
+        <v>3.094743804082221</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.996967190515576</v>
+        <v>3.010033444816052</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.972091484041776</v>
+        <v>3.985272493337014</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.911091597859475</v>
+        <v>3.924290336814238</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.060966412831547</v>
+        <v>3.074371540484378</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.817751550052428</v>
+        <v>3.831208843762646</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.890596245859399</v>
+        <v>2.904048534579509</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.989572404145264</v>
+        <v>2.003128450496867</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.277755274883084</v>
+        <v>1.267325639184932</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>175</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6494188226471707</v>
+        <v>0.6619411123227934</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.466416638254337</v>
+        <v>2.479326447830388</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.214405074514893</v>
+        <v>3.227412205932495</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.05090586509263062</v>
+        <v>-0.03779506071769134</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4096262160778252</v>
+        <v>-0.3965599617773492</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.408904670854959</v>
+        <v>1.422085680150197</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.640636742501876</v>
+        <v>1.654041870154707</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.007311989612866</v>
+        <v>2.020769283323084</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.09284517827232008</v>
+        <v>-0.07928913192071718</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9859809888531714</v>
+        <v>-0.9964106245513236</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>141</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0111688166638757</v>
+        <v>0.001353473011747042</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.923356861152008</v>
+        <v>1.93626667072806</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.8192682963993931</v>
+        <v>0.8322754278169953</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.949521429006893</v>
+        <v>0.9625005714053572</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.298119644221309</v>
+        <v>-0.2850088398463697</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7085421516503843</v>
+        <v>0.7215850479447496</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.922290856402043</v>
+        <v>-2.909224602101567</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5525948225594277</v>
+        <v>-0.5394138132641899</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.450474141365845</v>
+        <v>-3.437275402411082</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.59137946823774</v>
+        <v>-3.577974340584909</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.377693076243261</v>
+        <v>-2.364235782533044</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.052529777053863</v>
+        <v>-3.039077488333753</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.891224104310822</v>
+        <v>-4.87766805795922</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.35072263019056</v>
+        <v>-5.361152265888713</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>114</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.769719574526874</v>
+        <v>2.782241864202497</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.5962400033496706</v>
+        <v>-0.5833301937736195</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.868301692402405</v>
+        <v>-1.855294560984802</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.615241542251034</v>
+        <v>-2.60226239985257</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.733413802063687</v>
+        <v>-3.720370905769322</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.326919449160535</v>
+        <v>-7.313853194860059</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-6.916909865485891</v>
+        <v>-6.903728856190654</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.855102734124337</v>
+        <v>-7.841903995169574</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.950841954239984</v>
+        <v>-6.937436826587152</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.366826156299844</v>
+        <v>-5.353373867579734</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-7.541466732157033</v>
+        <v>-7.527910685805431</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.046131364793027</v>
+        <v>-9.056561000491179</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 3.321</t>
+          <t>X &gt; 3.32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.289001103187879</v>
+        <v>-7.275890298812939</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-6.991559165472218</v>
+        <v>-6.978516269177852</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.64772145417307</v>
+        <v>-10.63465519987259</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.73395247200218</v>
+        <v>-8.720771462706942</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.794952358184482</v>
+        <v>-8.781753619229718</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-12.0260299241648</v>
+        <v>-12.01262479651196</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.04030705800618</v>
+        <v>-11.02684976429596</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-11.00592390066075</v>
+        <v>-10.99247161194064</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-12.61665470208185</v>
+        <v>-12.60309865573024</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-13.5678391959799</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MVRV is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MVRV is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,105 +3904,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.7865</t>
+          <t>X &lt; 0.7866</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.37117854301625</v>
+        <v>11.3840883525923</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.35726221737204</v>
+        <v>13.37026934878964</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.05894392140811</v>
+        <v>17.07192306380657</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22.47290365871689</v>
+        <v>22.48601446309183</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20.38939321548017</v>
+        <v>20.40243611177453</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>23.87608806963646</v>
+        <v>23.88915432393694</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>24.59938086133116</v>
+        <v>24.6125618706264</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>24.53838097514886</v>
+        <v>24.55157971410362</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30.83111293297807</v>
+        <v>30.8445180606309</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>34.19778818008906</v>
+        <v>34.21124547379928</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>33.0416951469583</v>
+        <v>33.05514743567841</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>32.6214405360134</v>
+        <v>32.63499658236501</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>35.25211424924206</v>
+        <v>35.2416846135439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.8739</t>
+          <t>X &lt; 0.874</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>347</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8206827172540017</v>
+        <v>0.8332050069296244</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.955506798814241</v>
+        <v>2.968416608390292</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.119715902015919</v>
+        <v>1.132723033433521</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.402706786784798</v>
+        <v>2.415685929183262</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.457945514075746</v>
+        <v>4.471056318450685</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.890834137670375</v>
+        <v>3.90387703396474</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.399760362761199</v>
+        <v>6.412826617061675</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.508945840060399</v>
+        <v>6.522126849355637</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.871577077797397</v>
+        <v>5.88477581675216</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.462374082971202</v>
+        <v>6.475779210624033</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.833989634734316</v>
+        <v>6.847446928444533</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.003819477958714</v>
+        <v>6.017271766678824</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.871749305054152</v>
+        <v>5.885305351405755</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.274208389491818</v>
+        <v>7.263778753793666</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>548</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.06130620533747333</v>
+        <v>0.07382849501309607</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.369440621570291</v>
+        <v>1.382350431146342</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2446449076744344</v>
+        <v>0.2576520390920365</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.469788551230842</v>
+        <v>1.482767693629306</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.573703102582023</v>
+        <v>2.586813906956962</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.506181536648057</v>
+        <v>2.519224432942423</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.063783585799129</v>
+        <v>4.076849840099605</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.05645420161617</v>
+        <v>5.069635210911407</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.265527308134601</v>
+        <v>4.278726047089364</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.240219641354848</v>
+        <v>5.253624769007679</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.582911572511726</v>
+        <v>5.596368866221944</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.704885970733059</v>
+        <v>4.718338259453169</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.919667856138531</v>
+        <v>3.933223902490134</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.716834443889262</v>
+        <v>4.70640480819111</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>635</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5249343832021083</v>
+        <v>-0.5124120935264855</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.06821641328245676</v>
+        <v>0.0811262228585079</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.429014498038534</v>
+        <v>-1.416007366620931</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.03891884574599658</v>
+        <v>-0.02593970334753237</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3675418289456047</v>
+        <v>0.380652633320544</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3500231367400062</v>
+        <v>0.3630660330343716</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.525131939152772</v>
+        <v>1.538198193453248</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.002830430135049</v>
+        <v>2.016011439430287</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.941830543952747</v>
+        <v>1.95502928290751</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.981469138452375</v>
+        <v>2.994874266105207</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.249156759016685</v>
+        <v>3.262614052726903</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.338658026598345</v>
+        <v>2.352110315318455</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.603442785732177</v>
+        <v>1.61699883208378</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.640565692811613</v>
+        <v>2.630136057113461</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>703</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.426581990195757</v>
+        <v>-1.414059700520134</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3354529004573052</v>
+        <v>-0.3225430908812541</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.441559160396707</v>
+        <v>-1.428552028979105</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1733259424407052</v>
+        <v>-0.160346800042241</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7107279491727638</v>
+        <v>0.7238387535477031</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8659223762198565</v>
+        <v>0.8789652725142219</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.34591127630177</v>
+        <v>2.358977530602246</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.874460452200211</v>
+        <v>2.887641461495448</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.955708076686484</v>
+        <v>2.968906815641247</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.097048041018439</v>
+        <v>4.11045316867127</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.319037248706543</v>
+        <v>4.332494542416761</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.357687831372033</v>
+        <v>3.371140120092143</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.226195667084319</v>
+        <v>2.239751713435922</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.329402063371987</v>
+        <v>3.318972427673835</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1525019456601555</v>
+        <v>-0.2027385725007846</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.423834220671921</v>
+        <v>1.370082750351401</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4941025130570935</v>
+        <v>0.4410111070313931</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.293023095246312</v>
+        <v>1.239019505271244</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.907391567269933</v>
+        <v>1.852050033946675</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.031905292774852</v>
+        <v>1.976621877757644</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.345771952863274</v>
+        <v>3.288740245261991</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.96685941260656</v>
+        <v>3.980040421901798</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.510454447826916</v>
+        <v>4.523653186781679</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.836870979848563</v>
+        <v>5.850276107501394</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.312396735375579</v>
+        <v>6.250169870643873</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.816586921850075</v>
+        <v>5.754905304927803</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.835726250299111</v>
+        <v>5.773524720893143</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.525909307970288</v>
+        <v>6.560454840081128</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2481878884310404</v>
+        <v>-0.3257436167412493</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7783069950885135</v>
+        <v>0.6965087478427208</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6039255886028769</v>
+        <v>0.5217620702305439</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.387948250412443</v>
+        <v>1.304544375079566</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.024360289896222</v>
+        <v>1.938972116741525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.718100934474101</v>
+        <v>2.631873341211765</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.683131720430111</v>
+        <v>2.683410327898315</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.482132919582774</v>
+        <v>3.393588591809227</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.167780561070181</v>
+        <v>4.077869396643294</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.500763560853237</v>
+        <v>4.408913410430245</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.132747529682554</v>
+        <v>5.03940282369576</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.220671358192575</v>
+        <v>5.127135499833571</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.290351032149019</v>
+        <v>5.195972192121097</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.205534918819943</v>
+        <v>6.173099899797904</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7396802672393221</v>
+        <v>-0.7641778331094571</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5511485252784851</v>
+        <v>0.5249343832021083</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1237752742076736</v>
+        <v>0.09765371227715747</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.795365319235529</v>
+        <v>0.7687996639089789</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.08620827704663</v>
+        <v>1.059151034793679</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.926749537319253</v>
+        <v>1.899205673870725</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.242114566504085</v>
+        <v>2.214277476646302</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.895030056260921</v>
+        <v>2.866473068462817</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.595770669687568</v>
+        <v>3.566653369465044</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.796668031098008</v>
+        <v>3.766969978763157</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.28396252004854</v>
+        <v>4.253786986081415</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.362041467304621</v>
+        <v>4.331797966114081</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.346556575208858</v>
+        <v>4.316093263461681</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.001632553673659</v>
+        <v>5.019061268176884</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8318069002703936</v>
+        <v>-0.8504812479256643</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4774424047582713</v>
+        <v>-0.4969359604561845</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9608606760684637</v>
+        <v>-0.9802229642177949</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5560681851294262</v>
+        <v>-0.5756441300401178</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4562013570022927</v>
+        <v>-0.4760517193133396</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4803023063892624</v>
+        <v>0.4599769960870717</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4289772665523444</v>
+        <v>0.4086348434174596</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7233984295234706</v>
+        <v>0.7026886429848176</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.303495035344881</v>
+        <v>1.282393398800792</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.88503875604119</v>
+        <v>1.863253423628549</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.776308950099192</v>
+        <v>1.754496066867617</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.724350690927707</v>
+        <v>1.702563849052261</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.643699470019129</v>
+        <v>1.621788379375772</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.111635158702072</v>
+        <v>2.126448257285041</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4978122950596173</v>
+        <v>-0.5137029157802573</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1115764845965543</v>
+        <v>-0.1281874161077496</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6958302839963295</v>
+        <v>-0.7122564405195249</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4813471128588347</v>
+        <v>-0.4978634714972046</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1683226948382313</v>
+        <v>-0.185189834618491</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3784283031994633</v>
+        <v>0.3613402213635837</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1592947148836998</v>
+        <v>0.1422871560171401</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6003740138061957</v>
+        <v>0.5829664888642441</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9544004307070253</v>
+        <v>0.9367660608706387</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.234043335908467</v>
+        <v>1.215978011992</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9508445428210663</v>
+        <v>0.9328571954109961</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7966849316510576</v>
+        <v>0.7787789443566382</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8481092992809494</v>
+        <v>0.8300303714582</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.404830842487293</v>
+        <v>1.417615635374766</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7940606275340585</v>
+        <v>-0.8062748822089887</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1299161477336241</v>
+        <v>-0.1428441054076544</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7385006685202242</v>
+        <v>-0.751241324445175</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3907205081220937</v>
+        <v>-0.4036057198199643</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4715978829069627</v>
+        <v>-0.4845831719353342</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2919887422933485</v>
+        <v>-0.3049979409832559</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.302637669338921</v>
+        <v>-0.315671560351511</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.07126549519416869</v>
+        <v>-0.08453252161923075</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2305848148779219</v>
+        <v>0.2171485352920328</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5128894897546203</v>
+        <v>0.4991026239132026</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.527754510055388</v>
+        <v>0.5139011514549523</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3007354329475689</v>
+        <v>0.2869896675206434</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3410223504435521</v>
+        <v>0.3271456267758381</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.099898449627425</v>
+        <v>1.109924061465591</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6835822364768802</v>
+        <v>-0.6936448884245081</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1783103624936118</v>
+        <v>-0.1889185213304145</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5932896314774965</v>
+        <v>-0.6038019551245952</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1774877691720604</v>
+        <v>-0.188162987200478</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.342736358757989</v>
+        <v>-0.3534532017033456</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.152564826477871</v>
+        <v>-0.1633131236994743</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2134865446430041</v>
+        <v>-0.2242322894496738</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2180535272479105</v>
+        <v>0.2070191550705545</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.400108598364433</v>
+        <v>0.3889750396879208</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.8878221315436576</v>
+        <v>0.8762988254532331</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7956231090672219</v>
+        <v>0.7840917751919818</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4606259094473373</v>
+        <v>0.4492404210985939</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.503635062223708</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.129307231698206</v>
+        <v>1.137490546614202</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4758594148963553</v>
+        <v>-0.4841109187132631</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.02827332406152294</v>
+        <v>-0.03696828420545017</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4814879968279939</v>
+        <v>-0.4900709503995841</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2896275071633241</v>
+        <v>-0.2982717154245904</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3262159891422556</v>
+        <v>-0.3349379178605574</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2871480175062189</v>
+        <v>-0.2958431999501556</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3100781870143692</v>
+        <v>-0.318783454857531</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1144469774966836</v>
+        <v>-0.1233116537933867</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1672577763703416</v>
+        <v>0.1582646957885956</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4219404428111844</v>
+        <v>0.4127020476525587</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2398488069872258</v>
+        <v>0.2306444122038229</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.2247575015168195</v>
+        <v>-0.2337758351943293</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1809337256141745</v>
+        <v>-0.1900435460459136</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4529174620934739</v>
+        <v>0.4598031736937855</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4085809683445731</v>
+        <v>-0.4151025021979748</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.0113437199542048</v>
+        <v>0.004459690593478172</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2905102151734553</v>
+        <v>-0.2973381991691753</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4699570567788456</v>
+        <v>-0.476706929918592</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.07363625944949348</v>
+        <v>0.06661462699481291</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1584264987008481</v>
+        <v>-0.165329455991035</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.156807043387559</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1363393190816922</v>
+        <v>0.1292494840881915</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6091981501479751</v>
+        <v>0.6019228436546626</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8437822208767116</v>
+        <v>0.8363078800069275</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5497915364977004</v>
+        <v>0.5423944471500803</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2745265828745644</v>
+        <v>0.2672305067923162</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4995763605121866</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7335548960630831</v>
+        <v>0.7388680570903219</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3865524003744198</v>
+        <v>-0.3918749346439441</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.007393824193833609</v>
+        <v>0.00176563933433016</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.09466980672316794</v>
+        <v>-0.1003073671606245</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2201076169026877</v>
+        <v>-0.2256919026462398</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1519855830818386</v>
+        <v>0.1462143455139326</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.08075091629745401</v>
+        <v>-0.08641466009510168</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2840806322418246</v>
+        <v>-0.2896867389123656</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1144469774966836</v>
+        <v>-0.1201633512852354</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.152635608640864</v>
+        <v>0.1468178093417123</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3868321278725162</v>
+        <v>0.3808416934849319</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1327355519563298</v>
+        <v>0.1268075749283852</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2261374331163708</v>
+        <v>-0.2319418930059669</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2487250740902951</v>
+        <v>-0.2545691476408933</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1172365192828266</v>
+        <v>-0.1126325519187574</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2643462277921458</v>
+        <v>-0.2688145341127495</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.133657766507568</v>
+        <v>-0.1383110399665526</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2504504867262156</v>
+        <v>-0.2551026750198844</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7214190381079533</v>
+        <v>-0.7259091918570064</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3672506214436169</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5362912695263518</v>
+        <v>-0.5408678960456044</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7012094290826241</v>
+        <v>-0.7057423048579992</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5963138549115072</v>
+        <v>-0.6009242411316507</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2806200347167618</v>
+        <v>-0.2853413556941717</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.003152888232925477</v>
+        <v>-0.008041560281093041</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1896004678284839</v>
+        <v>-0.1944489188402869</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3001915750721196</v>
+        <v>-0.3050036766764279</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3428101757054662</v>
+        <v>-0.3476478143878197</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1073628749409394</v>
+        <v>-0.1035184791273309</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3213</v>
+        <v>3214</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4165629327332212</v>
+        <v>-0.4201785034193861</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2135390649571818</v>
+        <v>-0.2173346096490221</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1884662477112684</v>
+        <v>-0.1922998649423704</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7239557727543797</v>
+        <v>-0.7276161067003457</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.252555239926366</v>
+        <v>-0.2564023919530101</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3417461822224084</v>
+        <v>-0.3455465077164632</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.502793917941176</v>
+        <v>-0.5065524219716053</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.456093332074083</v>
+        <v>-0.4599018974895515</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2514914685458365</v>
+        <v>-0.2553700928461922</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.05872823818110362</v>
+        <v>-0.06272986029011207</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2771585150068958</v>
+        <v>-0.281109130460834</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2564608183827346</v>
+        <v>-0.2604175963045421</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1925873775789242</v>
+        <v>-0.1965963969729287</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.1742785300918896</v>
+        <v>-0.1710928185241229</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2087283026352864</v>
+        <v>-0.2115163233601152</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1348976642026543</v>
+        <v>-0.1377963239496722</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04290951263246257</v>
+        <v>0.03993575036344765</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3971854080721471</v>
+        <v>-0.4000246836394226</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1573155844055805</v>
+        <v>-0.1602560063976384</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2544906214221498</v>
+        <v>-0.2573879351462836</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3819602201019734</v>
+        <v>-0.3848263155467819</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3048778776795658</v>
+        <v>-0.3077935955037248</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1442519135909066</v>
+        <v>-0.1472196765067508</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.04969904583730766</v>
+        <v>0.04662638487662463</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1091896051496022</v>
+        <v>-0.1122284091459775</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.02891481903808568</v>
+        <v>-0.03197695579380877</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.05051713594427554</v>
+        <v>-0.0535975152799395</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.06883482162272969</v>
+        <v>0.07119666527817969</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3831400647232002</v>
+        <v>-0.3852760867931408</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3194785810774192</v>
+        <v>-0.3217025737951431</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.07983559472577895</v>
+        <v>-0.08214510981677137</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4693177352680848</v>
+        <v>-0.4715132296297284</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.0911473137847878</v>
+        <v>-0.09347354162850507</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3417986695578676</v>
+        <v>-0.3440427614649053</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4112367813862434</v>
+        <v>-0.4134661325296705</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.355644847852993</v>
+        <v>-0.3579110987191854</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3165863925088743</v>
+        <v>-0.3188674780238685</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.05108197601515485</v>
+        <v>-0.05347565462170678</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4375445082910332</v>
+        <v>-0.4398392195985394</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3309511173052329</v>
+        <v>-0.3332756536476111</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2836978039075575</v>
+        <v>-0.2860549881361862</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1874979130473093</v>
+        <v>-0.1855692919708574</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4758703816977672</v>
+        <v>-0.4776229460118486</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4806297255959748</v>
+        <v>-0.4824397574164578</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2565408979416546</v>
+        <v>-0.2584275995119256</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.578418715954534</v>
+        <v>-0.580213319447644</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3875760649120537</v>
+        <v>-0.3894434123660488</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5424374607155471</v>
+        <v>-0.5442525389536854</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6947905980252713</v>
+        <v>-0.6965678153860821</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6795756057441267</v>
+        <v>-0.6813747856968533</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.698076744114914</v>
+        <v>-0.6998740026966388</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5150358732698095</v>
+        <v>-0.5169150958504005</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7595473552811569</v>
+        <v>-0.7613676771297762</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6548120902978454</v>
+        <v>-0.6566609871126801</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5364852616810651</v>
+        <v>-0.5383829015871768</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3263981474521458</v>
+        <v>-0.3247341875209955</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3440562675501084</v>
+        <v>-0.3455413327100203</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3828942228813048</v>
+        <v>-0.3844180827599288</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3869774139643667</v>
+        <v>-0.3885128526155128</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7261749661576786</v>
+        <v>-0.7276161067003457</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.523971261234955</v>
+        <v>-0.5254837635179825</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6961596497337155</v>
+        <v>-0.6976176805869514</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7663846352689703</v>
+        <v>-0.7678271127055183</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8422008857687615</v>
+        <v>-0.8436378320749256</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8347246483606483</v>
+        <v>-0.8361662321887664</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6198380372295702</v>
+        <v>-0.6213639302914871</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7557729857565931</v>
+        <v>-0.7572692684833129</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6255874491844438</v>
+        <v>-0.6271185741738137</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5995837227467078</v>
+        <v>-0.6011353805252568</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3617079849630258</v>
+        <v>-0.3602920261685725</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 2.622</t>
+          <t>X &lt; 2.621</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2759092811392208</v>
+        <v>-0.277168339850796</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2629205679775097</v>
+        <v>-0.2642246156784367</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2737844960835574</v>
+        <v>-0.2750963760585279</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.4990858955384923</v>
+        <v>-0.5003356336502307</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3361671154701682</v>
+        <v>-0.3374742454695365</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4472443737347405</v>
+        <v>-0.4485152624326503</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5969798460544027</v>
+        <v>-0.5982139778643543</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5208947019489116</v>
+        <v>-0.5221615057680609</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5145290777612033</v>
+        <v>-0.5157997899328635</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3181581011831511</v>
+        <v>-0.3195031033902609</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.402277362273999</v>
+        <v>-0.4036060238254464</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3001483418272102</v>
+        <v>-0.3015038537415435</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3348245971585158</v>
+        <v>-0.3361823578369822</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.123161688947782</v>
+        <v>-0.1220159514278336</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2561854586074759</v>
+        <v>-0.2572489304043089</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2668646524040028</v>
+        <v>-0.267960604347401</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3353829823007572</v>
+        <v>-0.3364701776220187</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5034468250492949</v>
+        <v>-0.5044880316050424</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2986737222354847</v>
+        <v>-0.2997804067957262</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4037820905891181</v>
+        <v>-0.4048555548921371</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4483368540589154</v>
+        <v>-0.449401103443698</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4062038588743633</v>
+        <v>-0.4072897385946845</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4789982393106555</v>
+        <v>-0.48006703372765</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2978992977290744</v>
+        <v>-0.2990342508046311</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3316104338165999</v>
+        <v>-0.3327416125606959</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2565419668279958</v>
+        <v>-0.2576925673024348</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2707455659848108</v>
+        <v>-0.2719021541711015</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.08461245396858175</v>
+        <v>-0.0836459362125197</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3877</v>
+        <v>3878</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1798136415467368</v>
+        <v>-0.1807361281956261</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1579818483195154</v>
+        <v>-0.1589401698706752</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2046131500588899</v>
+        <v>-0.2055672599603184</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3691129715317274</v>
+        <v>-0.3700228503615577</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.250302968246821</v>
+        <v>-0.2512538427383504</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.350632524545567</v>
+        <v>-0.3515525655285998</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3441561557570907</v>
+        <v>-0.3450799102972937</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3080299525952412</v>
+        <v>-0.3089721394761042</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4321791190588513</v>
+        <v>-0.4330909504537317</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2890573716807765</v>
+        <v>-0.290022308839923</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3505672445550232</v>
+        <v>-0.3515206272301654</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2502063003955897</v>
+        <v>-0.2511854067369086</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.166078803852507</v>
+        <v>-0.1670879018540603</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.08233678678235634</v>
+        <v>-0.08150603455648309</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3929</v>
+        <v>3930</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1342297966178947</v>
+        <v>-0.1349865352262114</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2354356834914029</v>
+        <v>-0.2361914183724068</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2866826702276768</v>
+        <v>-0.287431742303994</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.320376428209272</v>
+        <v>-0.3211153698409959</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.08326456784239866</v>
+        <v>-0.0840722159057421</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1782979199021</v>
+        <v>-0.1790773468338998</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1475762741498272</v>
+        <v>-0.1483651796735046</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1942901013360014</v>
+        <v>-0.195074598595447</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2413173810619682</v>
+        <v>-0.2420912485635398</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.16213104653594</v>
+        <v>-0.1629383026973557</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1746383083089427</v>
+        <v>-0.1754458922971267</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1259830156321087</v>
+        <v>-0.1268028622434016</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.07394296089682229</v>
+        <v>-0.07478282672756364</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.03747099820277811</v>
+        <v>0.03812227257699163</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1459615439107012</v>
+        <v>-0.1465786811367664</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2124956097186796</v>
+        <v>-0.2131164344191632</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2170371331142036</v>
+        <v>-0.2176620568213252</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1987732358065415</v>
+        <v>-0.1994014418811645</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.09528169534431896</v>
+        <v>-0.09594294298618422</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1611346879889126</v>
+        <v>-0.161776001821849</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1567435694310362</v>
+        <v>-0.1573873696635815</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2077955303522785</v>
+        <v>-0.2084326574337609</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2046558622276109</v>
+        <v>-0.2052948667146239</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1602116290561071</v>
+        <v>-0.160872774948615</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1998722180747379</v>
+        <v>-0.2005262807002097</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1513705989775431</v>
+        <v>-0.1520367720091969</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1042133115241057</v>
+        <v>-0.1048969581327768</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.06694536452788213</v>
+        <v>-0.06638220421820051</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02829887797889796</v>
+        <v>-0.02883736486345612</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1075025931991433</v>
+        <v>-0.1080383785782644</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1401397329447178</v>
+        <v>-0.1406717648912021</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1209357553566903</v>
+        <v>-0.1214714838480688</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.002220470187239698</v>
+        <v>0.00164817733008249</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06061925023909964</v>
+        <v>-0.06117306070802186</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01787645581386954</v>
+        <v>0.01730191805311421</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.06150120164619466</v>
+        <v>-0.0620610957671488</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08380322787368044</v>
+        <v>-0.08435847259536189</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.07165246566953698</v>
+        <v>-0.07221989203519996</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08768836699508142</v>
+        <v>-0.08825421127565392</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.03927506884338072</v>
+        <v>-0.0398529209295404</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.004057918630785196</v>
+        <v>0.003464568810514379</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.04310434000732499</v>
+        <v>0.04354941540871238</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4037</v>
+        <v>4038</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.0003888402838470029</v>
+        <v>-4.710928034512563e-05</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.06697785068472939</v>
+        <v>-0.06741076557349146</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.02853676625303336</v>
+        <v>-0.02898267110946051</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03308191783789738</v>
+        <v>-0.03352583512059226</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01038924118517315</v>
+        <v>0.009929885450546294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02469825547161975</v>
+        <v>-0.02514668605048342</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1018899630941377</v>
+        <v>0.1014093124589266</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.01927179569153736</v>
+        <v>0.01880745491352087</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1203653770243918</v>
+        <v>0.1198752984763658</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1253116815198041</v>
+        <v>0.1248130583924905</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.08298384251243363</v>
+        <v>0.0824937503927643</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1065626884289514</v>
+        <v>0.1060668133304503</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1707931150836544</v>
+        <v>0.1702775925160296</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1868842930039278</v>
+        <v>0.1872021965057726</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07744616911848823</v>
+        <v>-0.07777723700811379</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01667599616825299</v>
+        <v>0.01631092521221689</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.05226659949298096</v>
+        <v>0.05188998526798372</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07318054389214979</v>
+        <v>0.07279948799587999</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1373723433181553</v>
+        <v>0.1369717532243797</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1045209168554138</v>
+        <v>0.104130194760053</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2051753419809117</v>
+        <v>0.2047591513295828</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1937414556917432</v>
+        <v>0.1933247579478561</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.220074148854799</v>
+        <v>0.2196503821742795</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1947876063872513</v>
+        <v>0.1943641676655048</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1759866884080452</v>
+        <v>0.1755663053767478</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1504717613915787</v>
+        <v>0.1500576889363359</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2114950079866844</v>
+        <v>0.2110629164244529</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2537546691895756</v>
+        <v>0.2539847365451422</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 3.321</t>
+          <t>X &lt; 3.32</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.09509402997378658</v>
+        <v>-0.09532693608449705</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03779322883911362</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.005361760355476974</v>
+        <v>-0.005626552678599239</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03239553835240372</v>
+        <v>-0.03265323687205068</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1492264422782839</v>
+        <v>0.1489217312622557</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1431718600437932</v>
+        <v>0.1428699406802139</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2180952455865821</v>
+        <v>0.2177745092124113</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1789395140605379</v>
+        <v>0.1786258968220977</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1802332271499196</v>
+        <v>0.1799188546378829</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2465072019594459</v>
+        <v>0.2461723549419332</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2263572840791994</v>
+        <v>0.2260262030748805</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2257074237440122</v>
+        <v>0.225376523164023</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2588031733760303</v>
+        <v>0.2584619841507134</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2781686377781298</v>
+        <v>0.2783146501739466</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
+++ b/workspaces/btc_daily_14days/on_chain/mvrv.xlsx
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.8303</t>
+          <t>X ≈ 0.8305</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.3886661290633882</v>
+        <v>-0.219569272641138</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2789188733224677</v>
+        <v>0.484666182122325</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.768684384766978</v>
+        <v>-2.572011090528207</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.260406486957635</v>
+        <v>-2.062571855116602</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.280843313393085</v>
+        <v>-1.028236382556159</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.36364987217447</v>
+        <v>-1.136965948334506</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.8286264385086497</v>
+        <v>1.088079852050683</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.742241702042584</v>
+        <v>1.004440860861543</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0778000119520712</v>
+        <v>0.2055387442939107</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.306687960531775</v>
+        <v>-0.9986692404214352</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.891389694715713</v>
+        <v>-1.584184633815219</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.617387198980779</v>
+        <v>-2.670724533909762</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.657803338386771</v>
+        <v>-2.303126509069926</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.672130342096139</v>
+        <v>-1.291151232487387</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.9177</t>
+          <t>X ≈ 0.9178</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>201</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.232989703272267</v>
+        <v>-1.26208402252356</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.352200438850922</v>
+        <v>-1.353391253042872</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.249566987198484</v>
+        <v>-1.249729460724019</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1280408888381217</v>
+        <v>-0.1285314519199474</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6654339931203097</v>
+        <v>-0.6170176326219661</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1277455702533032</v>
+        <v>0.1516511375499334</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.04289375754515845</v>
+        <v>0.0908118278221437</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.556900373823616</v>
+        <v>2.606078084721766</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.503289941920947</v>
+        <v>1.576448099913733</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.139632236064962</v>
+        <v>3.238874956398696</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.433199058620822</v>
+        <v>3.533029010439861</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.474237998551445</v>
+        <v>2.597866476667541</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.5629108808538632</v>
+        <v>0.7115572587757413</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2914358573251121</v>
+        <v>0.4634346168917745</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>87</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.189726054006769</v>
+        <v>-4.218846658178272</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.088407333807496</v>
+        <v>-8.089669709590119</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-11.92125656313146</v>
+        <v>-11.92152281626088</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-9.502877876477356</v>
+        <v>-9.503449681118397</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-13.48237802126121</v>
+        <v>-13.43407275164368</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-13.18933714369955</v>
+        <v>-13.16552830851074</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-14.42511011655814</v>
+        <v>-14.37728756307317</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-17.19049807377427</v>
+        <v>-17.14142798029923</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-12.6646315106949</v>
+        <v>-12.59154241652217</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-11.22088690512861</v>
+        <v>-11.12170171457743</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.428399023187</v>
+        <v>-11.3286134443254</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.54572759207398</v>
+        <v>-12.42213042625123</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-12.96906479289135</v>
+        <v>-12.82043364675345</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.44797055887014</v>
+        <v>-10.27597179930348</v>
       </c>
     </row>
     <row r="9">
@@ -731,150 +731,150 @@
         <v>68</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-9.796875453680997</v>
+        <v>-9.37976988181606</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.078073630599654</v>
+        <v>-3.772508840351044</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.540023136743997</v>
+        <v>0.1722644009553562</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.411398151805251</v>
+        <v>1.809936986525535</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.918270230446261</v>
+        <v>5.022463419386334</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.68332422958062</v>
+        <v>9.057906686334846</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.00291022666346</v>
+        <v>12.74561755081295</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.00750494303356</v>
+        <v>13.06194644594134</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12.41836759541678</v>
+        <v>13.82792173126317</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.51067651172663</v>
+        <v>15.26947949273429</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>14.31043540966388</v>
+        <v>14.410284306674</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.87942737129685</v>
+        <v>13.00306530163088</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.052764646594611</v>
+        <v>8.201411778879937</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.751488535112209</v>
+        <v>9.923487294679198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 1.179</t>
+          <t>X ≈ 1.18</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.788819048461569</v>
+        <v>7.049982893897443</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>11.29113241620334</v>
+        <v>10.47444953086741</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.3032848209611</v>
+        <v>9.707058002128392</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.430626381055333</v>
+        <v>7.170144408799494</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.498212324280018</v>
+        <v>5.897705200990309</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.43522217666046</v>
+        <v>5.403293189767275</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.806742670568759</v>
+        <v>5.347967946147612</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>10.4300736195343</v>
+        <v>7.199053957004118</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13.67511394191159</v>
+        <v>10.26219018596496</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>16.11908717515692</v>
+        <v>12.52514332923452</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.56837368185137</v>
+        <v>14.64258614284326</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>19.71076924603896</v>
+        <v>15.90239032631462</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>26.35591145591931</v>
+        <v>21.3582769436391</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>25.39319976505924</v>
+        <v>19.71600895450593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 1.267</t>
+          <t>X ≈ 1.268</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6468411260043609</v>
+        <v>-0.8281546383426388</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.03097735708711</v>
+        <v>-1.188090133284426</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7356255097488216</v>
+        <v>0.5588446612754865</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.488088200749417</v>
+        <v>1.300349497597132</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.184593057565252</v>
+        <v>2.03434194685935</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.342594727491829</v>
+        <v>4.141989850999302</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.164121864007662</v>
+        <v>1.023229786238744</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.932677403124984</v>
+        <v>1.780638616069332</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.968647590122735</v>
+        <v>2.661097199593222</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.7366026154239833</v>
+        <v>0.3082166310106587</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.939389362933802</v>
+        <v>1.327317773688499</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.521755131388275</v>
+        <v>2.914536498821043</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.720799324514424</v>
+        <v>3.130999367364254</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.184925067620348</v>
+        <v>4.603285819593758</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.901084097761149</v>
+        <v>-2.721082289021908</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3105895185560641</v>
+        <v>-0.08485009147744194</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.96586510499197</v>
+        <v>-1.744410864602266</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.835639961403508</v>
+        <v>-1.614526823387486</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.214265648952981</v>
+        <v>-2.947657820879591</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.656387417637042</v>
+        <v>-1.409049517250338</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06042550799583779</v>
+        <v>0.2180581066040759</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.312841982671209</v>
+        <v>0.5961072027610115</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.092195960602311</v>
+        <v>1.403016450164202</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6624452314991558</v>
+        <v>1.001128797619167</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4577440732390485</v>
+        <v>0.7969883500832609</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4921222255943718</v>
+        <v>0.8551550874481535</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.07197137228106243</v>
+        <v>0.4599971608842424</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5426291119464679</v>
+        <v>-0.1348398336405765</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>258</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.318125332860021</v>
+        <v>-1.347321127212652</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-6.030086619722127</v>
+        <v>-6.031273406166783</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.812454903701969</v>
+        <v>-6.81260829370629</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.845020457788117</v>
+        <v>-7.84551495016612</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.770906910108614</v>
+        <v>-8.722360990342843</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.31074218279911</v>
+        <v>-7.286784773849497</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.333437038189132</v>
+        <v>-9.285425359198811</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-10.96329637965047</v>
+        <v>-10.91404881725675</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-11.02427853617324</v>
+        <v>-10.95102142639355</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.385825239479757</v>
+        <v>-8.286477914185184</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.69130159153848</v>
+        <v>-11.59139355551981</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-12.43211723763277</v>
+        <v>-12.30842061660453</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-12.85226809094618</v>
+        <v>-12.70357854316835</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-13.40172623916918</v>
+        <v>-13.22972747960252</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>174</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.691497762569092</v>
+        <v>2.662301968216461</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.379162244217788</v>
+        <v>3.377975457773132</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.834965572106412</v>
+        <v>1.834812182102091</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2410527846604325</v>
+        <v>0.2405582922824294</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.576326449955417</v>
+        <v>2.624872369721189</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5745753824784714</v>
+        <v>-0.5506179735288583</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.383423672779251</v>
+        <v>-2.335411993788931</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.55164174185321</v>
+        <v>-0.5023941794594933</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.336761829410342</v>
+        <v>-2.263504719630646</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.910818556774821</v>
+        <v>-4.811471231480247</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.839657646069362</v>
+        <v>-6.739749610050687</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-7.954704781070362</v>
+        <v>-7.831008160042117</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.650717703349422</v>
+        <v>-6.502028155571594</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.275556765766432</v>
+        <v>-5.103558006199769</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>260</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.865531415149825</v>
+        <v>-2.894727209502456</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2459482774442492</v>
+        <v>-0.2471350638889049</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.025335046814668</v>
+        <v>-1.025488436818989</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2587362506196769</v>
+        <v>0.2582417582416738</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.587245610168154</v>
+        <v>-2.538699690402382</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.98217927284076</v>
+        <v>-4.958221863891147</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.528428093645395</v>
+        <v>-3.480416414655075</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.764727506662901</v>
+        <v>-4.715479944269184</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.825709663185762</v>
+        <v>-4.752452553406066</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.521782305669298</v>
+        <v>-4.422434980374724</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.418791156237269</v>
+        <v>-2.318883120218594</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.153643773112798</v>
+        <v>-3.029947152084553</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.189179241810734</v>
+        <v>-3.040489694032907</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.040366668507367</v>
+        <v>-0.868367908940705</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>204</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4602604400539931</v>
+        <v>0.4310646457013618</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.6607295745786885</v>
+        <v>-0.6619163610233443</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.90528335439177</v>
+        <v>0.9051299643874486</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.015900654843094</v>
+        <v>2.015406162465091</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9874150233159185</v>
+        <v>1.03596094308169</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.284789052950899</v>
+        <v>1.308746461900512</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7098826152535764</v>
+        <v>0.7578942942438971</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.183990442055077</v>
+        <v>3.233238004448793</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.142616128669438</v>
+        <v>2.215873238449134</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.724069881358957</v>
+        <v>4.823417206653531</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.538976566236137</v>
+        <v>3.638884602254812</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.172811708415423</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.418155201779214</v>
+        <v>1.590153961345877</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>210</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.804798255179932</v>
+        <v>1.775602460827301</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.622183590687591</v>
+        <v>1.620996804242935</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7512217297421202</v>
+        <v>0.7510683397377989</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.499505507621997</v>
+        <v>-1.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1330331559557862</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.740421031082604</v>
+        <v>-1.716463622132991</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.348940914158412</v>
+        <v>-1.300929235168091</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.720771462707049</v>
+        <v>-3.671523900313332</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.353182190658288</v>
+        <v>-2.279925080878591</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.631672415559422</v>
+        <v>-4.532325090264848</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.788754526200727</v>
+        <v>-5.688846490182051</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-7.659138278607308</v>
+        <v>-7.535441657579064</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-7.603098655730243</v>
+        <v>-7.454409107952415</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.901172529313286</v>
+        <v>-6.729173769746623</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>231</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3329367833184591</v>
+        <v>0.3037409889658278</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.453352421856259</v>
+        <v>0.4521656354116033</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.790182768703062</v>
+        <v>1.79002937869874</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.408596416712918</v>
+        <v>-2.409090909090921</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.412421389498753</v>
+        <v>4.460967309264525</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.246591955930377</v>
+        <v>1.27054936487999</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.594782029564648</v>
+        <v>1.642793708554969</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.859315117379637</v>
+        <v>2.908562679773354</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>5.395735558259403</v>
+        <v>5.4689926680391</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.411617627730372</v>
+        <v>5.510964953024946</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.908215170768976</v>
+        <v>4.008123206787651</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>7.851446798815218</v>
+        <v>8.000136346593045</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.748178120037466</v>
+        <v>3.920176879604128</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>185</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.04848359810192449</v>
+        <v>-0.0776793924545558</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.03804806954406814</v>
+        <v>-0.03923485598872389</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.810423788944078</v>
+        <v>2.810270398939757</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.48118947307298</v>
+        <v>3.480694980694977</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.321278298355665</v>
+        <v>1.369824218121437</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.078111787450204</v>
+        <v>1.102069196399817</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.249841815059206</v>
+        <v>-2.201830136068885</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.797991539927025</v>
+        <v>-3.748743977533309</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.561676399152439</v>
+        <v>-6.488419289372743</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.330514114401275</v>
+        <v>-6.231166789106702</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.994674732120934</v>
+        <v>-5.894766696102259</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.581918201387225</v>
+        <v>-7.45822158035898</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.24531229794388</v>
+        <v>-11.09662275016605</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-12.64119826933891</v>
+        <v>-12.46919950977225</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>154</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.793400824896885</v>
+        <v>-2.794587611341541</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.188172209651924</v>
+        <v>-3.188325599656245</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-10.2008042089207</v>
+        <v>-10.2012987012987</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-10.08974311266582</v>
+        <v>-10.04119719290005</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-9.143018433679934</v>
+        <v>-9.119061024730321</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.578378143595529</v>
+        <v>-8.530366464605208</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-9.694797436732919</v>
+        <v>-9.645549874339203</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-8.4570782945544</v>
+        <v>-8.383821184774703</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.358945142832155</v>
+        <v>-7.259597817537582</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.68511230458126</v>
+        <v>-1.561415683553015</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.105263157894669</v>
+        <v>-1.956573610116841</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.06852444038359806</v>
+        <v>0.2405231999502604</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>153</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.461308187397101</v>
+        <v>-3.490503981749733</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.80452042425177</v>
+        <v>-1.805707210696426</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.068682047202259</v>
+        <v>1.068528657197938</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7618771229347914</v>
+        <v>-0.7623716153127944</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.967807180178738</v>
+        <v>2.01635309994451</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.572370752297338</v>
+        <v>3.596328161246952</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.487660393031312</v>
+        <v>3.535672072021633</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.366996978002668</v>
+        <v>2.416244540396384</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.158283059817357</v>
+        <v>-1.058935734522784</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.016578989319378</v>
+        <v>-1.916670953300702</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6321782480032709</v>
+        <v>0.7558748690315156</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.826406479657173</v>
+        <v>2.975096027435001</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.523021268808954</v>
+        <v>-1.351022509242291</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>188</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.370147799252912</v>
+        <v>3.340952004900281</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.227046812572034</v>
+        <v>1.225860026127378</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.023764789519177</v>
+        <v>4.023611399514856</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.217819720341524</v>
+        <v>5.217325227963521</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.488040805543697</v>
+        <v>1.536586725309469</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.253499941561742</v>
+        <v>1.277457350511355</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.700704475912566</v>
+        <v>1.748716154902887</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.297465619359933</v>
+        <v>2.34671318175365</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.704568569220164</v>
+        <v>1.777825678999861</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.918479560124339</v>
+        <v>2.017826885418913</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.777608189098224</v>
+        <v>2.877516225116899</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.875816128687525</v>
+        <v>3.99951274971577</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.391835488140082</v>
+        <v>2.540525035917909</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.213315819217677</v>
+        <v>4.385314578784339</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>140</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.623773173391541</v>
+        <v>-4.652968967744172</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.806387837883889</v>
+        <v>-4.807574624328545</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.058302079781797</v>
+        <v>-3.058455469786118</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.213791221907712</v>
+        <v>-2.214285714285715</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.533633510710921</v>
+        <v>1.582179430476693</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.454706745368284</v>
+        <v>-2.430749336418671</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.577914319849803</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.496039333515469</v>
+        <v>-4.422782223735773</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.488815272702482</v>
+        <v>-2.389467947407908</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-8.40780214524834</v>
+        <v>-8.307894109229665</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.659138278607308</v>
+        <v>-7.535441657579064</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.936431989063607</v>
+        <v>-5.787742441285779</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>89</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.166309288961315</v>
+        <v>-4.195505083313947</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.901090887643186</v>
+        <v>-6.902277674087841</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.295862272398097</v>
+        <v>-7.296015662402418</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.918446117573851</v>
+        <v>-4.918940609951854</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-12.19830870437741</v>
+        <v>-12.14976278461164</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-8.530148157888384</v>
+        <v>-8.506190748938771</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.98564503400849</v>
+        <v>-11.93763335501817</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-13.57630918341314</v>
+        <v>-13.52706162101943</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.884482351172</v>
+        <v>-15.81122524139231</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-18.98159215873775</v>
+        <v>-18.88224483344317</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-13.56831578890806</v>
+        <v>-13.46840775288938</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-13.53393763655274</v>
+        <v>-13.41024101552449</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-10.58330197301215</v>
+        <v>-10.43461242523432</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.863184300313833</v>
+        <v>-5.691185540747171</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>79</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.746932070731468</v>
+        <v>5.717736276378837</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.135745977667789</v>
+        <v>4.134559191223133</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.385607685568409</v>
+        <v>-6.385761075572731</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.521205326790245</v>
+        <v>-7.521699819168248</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.793672095075813</v>
+        <v>-6.745126175310041</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-7.762120850250852</v>
+        <v>-7.738163441301239</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-4.049362855086571</v>
+        <v>-4.00135117609625</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.313899853303759</v>
+        <v>-8.264652290910043</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7.109059225016267</v>
+        <v>-7.035802115236571</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.427332451725945</v>
+        <v>-5.327985126431372</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.568742470745633</v>
+        <v>-0.4688344347269577</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.7314584664198236</v>
+        <v>0.8551550874480682</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.486160741324042</v>
+        <v>-3.337471193546214</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.994602306287241</v>
+        <v>-1.822603546720579</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>66</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.579690030071703</v>
+        <v>3.550494235719071</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>6.513958482462336</v>
+        <v>6.51277169601768</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.119187097707346</v>
+        <v>6.119033707703025</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>12.3100183019019</v>
+        <v>12.3095238095239</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.25657723365455</v>
+        <v>10.30512315342032</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>13.58425429359281</v>
+        <v>13.60821170254242</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.954089388871999</v>
+        <v>9.00210106786232</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>17.57792983599436</v>
+        <v>17.62717739838808</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>17.51694767947158</v>
+        <v>17.59020478925128</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>16.66702888314173</v>
+        <v>16.7663762084363</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>19.49263075518455</v>
+        <v>19.59253879120322</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>18.01185739238837</v>
+        <v>18.13555401341662</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.561403508772</v>
+        <v>14.71009305654983</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>13.27198764384695</v>
+        <v>13.44398640341361</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>56</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.48687350835327</v>
+        <v>-4.487026898357591</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.247919224996643</v>
+        <v>2.296465144762415</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.350657108721627</v>
+        <v>7.399904671115344</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.932532095056047</v>
+        <v>2.005789204835743</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.698004578535553</v>
+        <v>2.821701199563798</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.063568010936422</v>
+        <v>4.212257558714249</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.503589375448719</v>
+        <v>2.675588135015381</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>46</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.214736143378694</v>
+        <v>6.185540349026063</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.951376137271389</v>
+        <v>8.950189350826733</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.73051779599461</v>
+        <v>10.73036440599029</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>10.86074293958297</v>
+        <v>10.86024844720497</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.800714256052494</v>
+        <v>3.849260175818266</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.098088285687581</v>
+        <v>4.122045694637194</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.361204013377936</v>
+        <v>8.409215692368257</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.894135369591197</v>
+        <v>7.943382931984914</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.485327126111834</v>
+        <v>3.55858423589153</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.917118915434685</v>
+        <v>-1.81721087941601</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2911722803989036</v>
+        <v>0.4148689014271483</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.566673600998541</v>
+        <v>8.715363148776369</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.09675707731197036</v>
+        <v>0.2687558368786327</v>
       </c>
     </row>
     <row r="29">
@@ -1771,98 +1771,98 @@
         <v>52</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.288314738696364</v>
+        <v>3.259118944343733</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.015179046675044</v>
+        <v>-6.0163658331197</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.40995043143014</v>
+        <v>-6.410103821434461</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.335659327542885</v>
+        <v>3.335164835164882</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>12.41275438983175</v>
+        <v>12.46130030959753</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.71012841946684</v>
+        <v>12.73408582841645</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>14.54849498327759</v>
+        <v>14.59650666226791</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.312195570260087</v>
+        <v>8.361443132653804</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>14.02044418296808</v>
+        <v>14.09370129274777</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.324371540484378</v>
+        <v>9.423718865778952</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>12.96582422837803</v>
+        <v>13.0657322643967</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.154048534579509</v>
+        <v>9.277745155607754</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.81082075818923</v>
+        <v>6.959510305967058</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.959633331492633</v>
+        <v>9.131632091059295</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 2.928</t>
+          <t>X ≈ 2.927</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>41</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.261403835412331</v>
+        <v>-1.290599629764962</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.0054588520115</v>
+        <v>2.004272065566845</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.488736247744342</v>
+        <v>6.48858285774002</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.49701017182043</v>
+        <v>11.49651567944242</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.236401332494694</v>
+        <v>-1.187855412728922</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.49999708738433</v>
+        <v>1.523954496333943</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.023737662125747</v>
+        <v>-0.9757259831354261</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.490806305912514</v>
+        <v>-1.441558743518797</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.326260318052505</v>
+        <v>3.399517427832201</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.03731713147875126</v>
+        <v>0.1366644567733246</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.606408417025342</v>
+        <v>-2.506500381006667</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.572030264670019</v>
+        <v>-2.448333643641774</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.992181117983506</v>
+        <v>-2.843491570205678</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.08351863848857</v>
+        <v>-9.911519878921908</v>
       </c>
     </row>
     <row r="31">
@@ -1872,101 +1872,101 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>16.23988817511302</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>14.65671108995716</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>11.13797310164246</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>9.279715271598775</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>10.77860800190522</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.06910277844112</v>
+        <v>11.0513935207241</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.07530151008407</v>
+        <v>20.36573743149869</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>17.57792983599436</v>
+        <v>19.89990467111534</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14.48664464916855</v>
+        <v>13.61293206197855</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>9.664103481163522</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.4320246945785</v>
+        <v>12.58496303362747</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.46640284693382</v>
+        <v>12.64312977099237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>13.04625199362042</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.27198764384691</v>
+        <v>12.49701670644387</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 3.102</t>
+          <t>X ≈ 3.101</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.401436910642119</v>
+        <v>3.37224111628953</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>4.730240501721823</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>13.1601853151762</v>
+        <v>10.21885545458359</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.34923398817632</v>
+        <v>13.28991596638656</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.9874150233159185</v>
+        <v>3.97713741366988</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.225965523539287</v>
+        <v>7.191099403077089</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.02360810544958</v>
+        <v>13.01279625502806</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.556539461662801</v>
+        <v>9.605787024056475</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>24.20143965808124</v>
+        <v>27.21587323844913</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.35152086175134</v>
+        <v>26.39204465763424</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.20564323290291</v>
+        <v>23.24672773950986</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.29884491467001</v>
+        <v>20.36371800628648</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>19.81987053194487</v>
+        <v>22.90973655031089</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>17.10442971158313</v>
+        <v>20.21760494173807</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-11.74017528979363</v>
+        <v>-13.22439753917278</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>10.1924253756715</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>13.37011595878536</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>16.01372200560548</v>
+        <v>13.49999999999997</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>19.17913615621352</v>
+        <v>16.58217943047669</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>19.47651018584861</v>
+        <v>16.85496494929558</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>15.68809612287868</v>
+        <v>13.22288028864155</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>26.33213859020311</v>
+        <v>23.47133324254397</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>15.16004532256916</v>
+        <v>12.72007491912141</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>8.3248177668778</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>14.10542536797917</v>
+        <v>11.69210589077028</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.732396112927084</v>
+        <v>4.607415485278075</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.312245259613626</v>
+        <v>4.212257558714249</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>8.032730992158143</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534331</v>
+        <v>-0.7859738938524785</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-7.425435456931517</v>
+        <v>-5.817426841077321</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.820206841686556</v>
+        <v>-6.211164829392025</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-14.35664836476484</v>
+        <v>-12.97783251231525</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.771728748806133</v>
+        <v>0.3260217950086641</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.402436111774556</v>
+        <v>4.047083175896553</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.984392419175052</v>
+        <v>0.5381512246021103</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-3.375957397850151</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-6.861205869055908</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.273089489202341</v>
+        <v>6.108068998404924</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.068388330942128</v>
+        <v>5.903928550868855</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>9.410371150302716</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.682615629984063</v>
+        <v>9.01521322373889</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.575017946877267</v>
+        <v>5.815982223685289</v>
       </c>
     </row>
   </sheetData>
@@ -2210,157 +2210,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.7866</t>
+          <t>X &gt; 0.7868</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09532693608449705</v>
+        <v>-0.08174854173982027</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2328374535226985</v>
+        <v>-0.2191086817212451</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2735271858982742</v>
+        <v>-0.2596216505441333</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3493402039853279</v>
+        <v>-0.3352716542267018</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.46024006211006</v>
+        <v>-0.4467809139917165</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4176954992418018</v>
+        <v>-0.4039006684321791</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4891976994662812</v>
+        <v>-0.4757022572172716</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5041344055431836</v>
+        <v>-0.4905112860726888</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5030079746304139</v>
+        <v>-0.4898659915494292</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.6320906360314709</v>
+        <v>-0.6189641752005102</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.7012553977059923</v>
+        <v>-0.6879191474825461</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6777233059792493</v>
+        <v>-0.6892904871035697</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6692723908492866</v>
+        <v>-0.6569234307784768</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.722906351047051</v>
+        <v>-0.7109613690737504</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.874</t>
+          <t>X &gt; 0.8741</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3832</v>
+        <v>3843</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07519431401939869</v>
+        <v>-0.07235248878739498</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.267960604347401</v>
+        <v>-0.2670891694462085</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1022781401512916</v>
+        <v>-0.1019724095147723</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2181788176539783</v>
+        <v>-0.2175114011345514</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4039199537887015</v>
+        <v>-0.407139661646184</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3527722215587943</v>
+        <v>-0.3539232801068053</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.5796433540297983</v>
+        <v>-0.5823145165532608</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.5896763983132871</v>
+        <v>-0.5924310004876716</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5321910889791539</v>
+        <v>-0.5372758382293554</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5857912893864849</v>
+        <v>-0.5930774390339977</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6195734248162381</v>
+        <v>-0.6268154375113753</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.5445991922372357</v>
+        <v>-0.5542044292677133</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.5327944056712255</v>
+        <v>-0.544692047350857</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6577586710768273</v>
+        <v>-0.6714064005037912</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.9613</t>
+          <t>X &gt; 0.9615</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3631</v>
+        <v>3642</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.01110263865729166</v>
+        <v>-0.006691852246767382</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2079407181631012</v>
+        <v>-0.2071367480286028</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.03876807177990571</v>
+        <v>-0.03862832184508136</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2231685515267401</v>
+        <v>-0.2224221561571014</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3894434123660488</v>
+        <v>-0.3955566105297237</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3793720772884015</v>
+        <v>-0.3818256573580427</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6141049236873499</v>
+        <v>-0.6194639935492745</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7638603507229647</v>
+        <v>-0.7689549780074643</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6448685021465792</v>
+        <v>-0.6539311132339591</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.7920182595367891</v>
+        <v>-0.8045608084689135</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.8439213370087018</v>
+        <v>-0.8563949910638868</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7117119092156159</v>
+        <v>-0.7281655089198225</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5934489808823287</v>
+        <v>-0.614023763586836</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7103029013739288</v>
+        <v>-0.7340376592892142</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3544</v>
+        <v>3555</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09147643502651448</v>
+        <v>0.09639041726548214</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.01448682551043845</v>
+        <v>-0.014230878083211</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2529295858802527</v>
+        <v>0.252176691098434</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.004634696574477459</v>
+        <v>0.004708475255455369</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.06803107856980972</v>
+        <v>-0.07647056150668163</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.0649062305678072</v>
+        <v>-0.06897555028342595</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2750650106569381</v>
+        <v>-0.282774640371052</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3606104969121731</v>
+        <v>-0.3682784235209979</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3498009565078348</v>
+        <v>-0.3617870391450495</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5360048362392362</v>
+        <v>-0.5520738158299707</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.584087940085027</v>
+        <v>-0.6001128517013612</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4212041878813366</v>
+        <v>-0.4419840890020126</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2896457710502744</v>
+        <v>-0.3153014964038547</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4712574481566136</v>
+        <v>-0.5005219714745195</v>
       </c>
     </row>
     <row r="10">
@@ -2422,101 +2422,101 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3476</v>
+        <v>3487</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2849194524120477</v>
+        <v>0.2811850545862526</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.06500796814493981</v>
+        <v>0.05905931447033197</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.288004610373477</v>
+        <v>0.2537350609664415</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.0323361447015813</v>
+        <v>-0.0304952926729527</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.146013958032718</v>
+        <v>-0.1759048920775825</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1773572292128378</v>
+        <v>-0.2469589148059441</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.4761301188668909</v>
+        <v>-0.5368413650629122</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.5830017080503467</v>
+        <v>-0.6301812887700464</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.59958100873191</v>
+        <v>-0.6385006027779028</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8303587866597439</v>
+        <v>-0.8606099858851408</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8754652668350076</v>
+        <v>-0.8928306626476044</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6814006625718179</v>
+        <v>-0.7041760472936716</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4528459748477047</v>
+        <v>-0.4813859537365985</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6712421221676266</v>
+        <v>-0.703800615035874</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 1.223</t>
+          <t>X &gt; 1.224</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3355</v>
+        <v>3358</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.05035258173485602</v>
+        <v>0.02115678738222471</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3398686512932372</v>
+        <v>-0.3410554377378929</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1092677906641129</v>
+        <v>-0.1094211806684342</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3066185851341245</v>
+        <v>-0.3071130775121276</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4577729387062917</v>
+        <v>-0.4092270189405198</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.4879748471295713</v>
+        <v>-0.4640174381799582</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.8109222522563755</v>
+        <v>-0.7629105732660548</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9801945887173318</v>
+        <v>-0.930947026323615</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.114406072525604</v>
+        <v>-1.057258527658142</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.441650280364613</v>
+        <v>-1.374833386019283</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.540652901049924</v>
+        <v>-1.489634941357643</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.416855970751229</v>
+        <v>-1.342129311795006</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.419719193662253</v>
+        <v>-1.320372408102735</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.611271173838105</v>
+        <v>-1.488242376343464</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1246248665632734</v>
+        <v>0.1127849088642492</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2662446038092554</v>
+        <v>-0.2496729417155521</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.199274563762188</v>
+        <v>-0.1815171655960697</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4978093146329314</v>
+        <v>-0.4805344770702717</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.73926509464156</v>
+        <v>-0.6728519123145134</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.002577080837597</v>
+        <v>-0.9609373931656506</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.021324379417749</v>
+        <v>-0.9556086589005233</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.290503841146446</v>
+        <v>-1.223486948812067</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.549375179727264</v>
+        <v>-1.458414028420663</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.673700308510952</v>
+        <v>-1.556409550839078</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.911382997114153</v>
+        <v>-1.793542410120459</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.942967905444846</v>
+        <v>-1.801360496246161</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.967340394642157</v>
+        <v>-1.80060948186641</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.335272290589778</v>
+        <v>-2.14542803126642</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2794</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3823624232952767</v>
+        <v>0.3531666289426454</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2624671916010399</v>
+        <v>-0.2636539780456957</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.04879190491728025</v>
+        <v>-0.0489452949216016</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3838495100762387</v>
+        <v>-0.3843440024542417</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5284382757703625</v>
+        <v>-0.4798923560045907</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.9468838595926883</v>
+        <v>-0.9229264506430752</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.103176180204585</v>
+        <v>-1.055164501214264</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.427080901299846</v>
+        <v>-1.377833338906129</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.774390903205585</v>
+        <v>-1.701133793425889</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.872699105405161</v>
+        <v>-1.773351780110588</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.113191244338232</v>
+        <v>-2.013283208319557</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.150395053328644</v>
+        <v>-2.0266984323004</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.141054138567611</v>
+        <v>-1.992364590789784</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.487974179106999</v>
+        <v>-2.315975419540337</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2536</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5553615719893088</v>
+        <v>0.5261657776366775</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3243016618907717</v>
+        <v>0.3231148754461159</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6393094569464637</v>
+        <v>0.6391560669421423</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3752128339733147</v>
+        <v>0.3747183415953117</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3101094007514362</v>
+        <v>0.3586553205172081</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2994566327049668</v>
+        <v>-0.2754992237553537</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2658704620026811</v>
+        <v>-0.2178587830123604</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4569138691963488</v>
+        <v>-0.4076663068026321</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.833353438968345</v>
+        <v>-0.7600963291886487</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.210086115424382</v>
+        <v>-1.110738790129808</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.138762037091517</v>
+        <v>-1.038854001072842</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.104383884736194</v>
+        <v>-0.9806872637079493</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.051348618175787</v>
+        <v>-0.9026590703979593</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.377663441135368</v>
+        <v>-1.205664681568706</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2362</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3980001422006154</v>
+        <v>0.3688043478479841</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.09926112788361507</v>
+        <v>0.09807434143895932</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5512297939329827</v>
+        <v>0.5510764039286613</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.385095919739797</v>
+        <v>0.3846014273617939</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1431653844256502</v>
+        <v>0.191711304191422</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2791896291230103</v>
+        <v>-0.2552322201733972</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.109877973147853</v>
+        <v>-0.06186629415753231</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4499356093139326</v>
+        <v>-0.4006880469202159</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7226027785378122</v>
+        <v>-0.6493456687581158</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9374665367643615</v>
+        <v>-0.8381192114697882</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.7187976696223615</v>
+        <v>-0.6188896336036862</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.5997455121866011</v>
+        <v>-0.4760488911583565</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6388633426380181</v>
+        <v>-0.4901737948601905</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.090519733055018</v>
+        <v>-0.9185209734883557</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2102</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8016719808833486</v>
+        <v>0.7724761865307173</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1419606737376853</v>
+        <v>0.1407738872930295</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7462378141967321</v>
+        <v>0.7460844241924107</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4007255648260113</v>
+        <v>0.4002310724480083</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4808946225771251</v>
+        <v>0.5294405423428969</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3025312592531222</v>
+        <v>0.3264886682027353</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3129683785787734</v>
+        <v>0.360980057569094</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.0837684312715794</v>
+        <v>0.1330159936652962</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2150824217307417</v>
+        <v>-0.1418253119510453</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4941163465096992</v>
+        <v>-0.3947690212151258</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.50852254758626</v>
+        <v>-0.4086145115675848</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.283849438047298</v>
+        <v>-0.1601528170190534</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3234103769934364</v>
+        <v>-0.1747208292156088</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.096723251980983</v>
+        <v>-0.9247244924143203</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1898</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8383674257354059</v>
+        <v>0.8091716313827746</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2282350734513443</v>
+        <v>0.2270482870066886</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7291433514992605</v>
+        <v>0.7289899614949391</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.227124027226715</v>
+        <v>0.226629534848712</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.42645301996874</v>
+        <v>0.4749989397345118</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1969566597197385</v>
+        <v>0.2209140686693516</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2703074174187918</v>
+        <v>0.3183190964091125</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.2494482653563566</v>
+        <v>-0.2002007029626398</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4684915388443542</v>
+        <v>-0.3952344290646579</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.054975140232159</v>
+        <v>-0.9556278149375856</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.9435540645619085</v>
+        <v>-0.8436460285432332</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5403666392877255</v>
+        <v>-0.4166700182594809</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5917082196822676</v>
+        <v>-0.44301867190444</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.367026310235502</v>
+        <v>-1.19502755066884</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1688</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7181361021670654</v>
+        <v>0.688940307814434</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.05481730768143223</v>
+        <v>0.05363052123677647</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.726396633826873</v>
+        <v>0.7262432438225517</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4419298342872722</v>
+        <v>0.4414353419092691</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4960573428029562</v>
+        <v>0.544603262568728</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4379811354712189</v>
+        <v>0.4619385444208319</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4717541885273207</v>
+        <v>0.5197658675176413</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1824106632239975</v>
+        <v>0.2316582256177142</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2340217302656029</v>
+        <v>-0.1607646204859066</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6100068773063683</v>
+        <v>-0.5106595520117949</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3407743862774595</v>
+        <v>-0.2408663502587842</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3452625338503807</v>
+        <v>0.4689591548786254</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2805619175037961</v>
+        <v>0.4292514652816237</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6785365554924141</v>
+        <v>-0.5065377959257518</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1457</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7792075109893233</v>
+        <v>0.750011716636692</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.008368424215881021</v>
+        <v>-0.009555210660536773</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5577387085307848</v>
+        <v>0.5575853185264634</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8938663915837992</v>
+        <v>0.8933718992057962</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1248624202627511</v>
+        <v>-0.07631650049697924</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3097799690154446</v>
+        <v>0.3337373779650576</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2937037895708201</v>
+        <v>0.3417154685611408</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2419990340374625</v>
+        <v>-0.1927514716437457</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.126591348418849</v>
+        <v>-1.053334238639152</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.564705065819403</v>
+        <v>-1.46535774052483</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.014430246042544</v>
+        <v>-0.9145222100238684</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4996128349363573</v>
+        <v>-0.3759162139081127</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9197636882497662</v>
+        <v>-0.7710741404719386</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.380369836238749</v>
+        <v>-1.208371076672087</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1272</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8995871141197398</v>
+        <v>0.8703913197671085</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.004051809132775475</v>
+        <v>-0.005238595577431227</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2301076237222475</v>
+        <v>0.2299542337179261</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5175654717131337</v>
+        <v>0.5170709793351307</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3351894901875951</v>
+        <v>-0.2866435704218233</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1980335960512605</v>
+        <v>0.2219910050008735</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6636377021939026</v>
+        <v>0.7116493811842233</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2751854106084153</v>
+        <v>0.324432973002132</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.336111211323157</v>
+        <v>-0.2628541015434607</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8715645988479821</v>
+        <v>-0.7722172735534087</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2901022350956026</v>
+        <v>-0.1901941990769274</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5304394392722998</v>
+        <v>0.6541360603005444</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5819866991664355</v>
+        <v>0.7306762469442631</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2574078839841576</v>
+        <v>0.4294066435508199</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1118</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.739119747640963</v>
+        <v>0.7099239532883317</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3801697905341967</v>
+        <v>0.378983004089541</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7009619120403414</v>
+        <v>0.7008085220360201</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.99397775330312</v>
+        <v>1.993483260925117</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.008461008794193</v>
+        <v>1.057006928559964</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.484725914994563</v>
+        <v>1.508683323944176</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.936688185424288</v>
+        <v>1.984699864414608</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.648510418202846</v>
+        <v>1.697757980596563</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7825193171362415</v>
+        <v>0.8557764269159378</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.02204595908902007</v>
+        <v>0.1213932843835934</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5329083070900182</v>
+        <v>0.6328163431086935</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8356227742932774</v>
+        <v>0.959319395321522</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9521445506757544</v>
+        <v>1.100834098453582</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2834258180758198</v>
+        <v>0.4554245776424821</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>965</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.405094332159948</v>
+        <v>1.375898537807316</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7265507261427544</v>
+        <v>0.7253639396980986</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6426601704032606</v>
+        <v>0.6425067803989393</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.430916402074523</v>
+        <v>2.43042190969652</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8563574189270113</v>
+        <v>0.9049033386927832</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.153731448562098</v>
+        <v>1.177688857511711</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.690782747327013</v>
+        <v>1.738794426317334</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.534594932555827</v>
+        <v>1.583842494949543</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8518511180019601</v>
+        <v>0.9251082277816565</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.209186207682464</v>
+        <v>0.3085335329770373</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.9371275364689069</v>
+        <v>1.037035572487582</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8678787458190413</v>
+        <v>0.991575366847286</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6549817785159959</v>
+        <v>0.8036713262938235</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5698365997269903</v>
+        <v>0.7418353592936526</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>777</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9296373800190523</v>
+        <v>0.900441585666421</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6054525739565122</v>
+        <v>0.6042657875118564</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1754191968989076</v>
+        <v>-0.175572586903229</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.756607748491255</v>
+        <v>1.756113256113252</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.7035176805950485</v>
+        <v>0.7520636003608203</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.129591838930267</v>
+        <v>1.15354924787988</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.688382123164736</v>
+        <v>1.736393802155057</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.350013608078129</v>
+        <v>1.399261170471846</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6455308080547013</v>
+        <v>0.7187879178343977</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2043879882751582</v>
+        <v>-0.1050406629805849</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4918117543655569</v>
+        <v>0.5917197903842322</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1400895206204922</v>
+        <v>0.2637861416487368</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.234739182107603</v>
+        <v>0.3834287298854306</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3117259398666405</v>
+        <v>-0.1397271802999782</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>637</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.150167171977422</v>
+        <v>2.120971377624791</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.794868049086276</v>
+        <v>1.79368126264162</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4581814367017287</v>
+        <v>0.4580280466974074</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.629222906820694</v>
+        <v>2.628728414442691</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5210746410091431</v>
+        <v>0.569620560774915</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.917349769545339</v>
+        <v>1.941307178494952</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.303597024093918</v>
+        <v>2.351608703084239</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.775546223784403</v>
+        <v>1.848803333564099</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2976839423682094</v>
+        <v>0.3970312676627827</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.447770853181794</v>
+        <v>2.547678889200469</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.854205520450783</v>
+        <v>1.977902141479028</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.591040538408961</v>
+        <v>1.739730086186789</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.031846832277559</v>
+        <v>1.203845591844221</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>548</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.176018276034988</v>
+        <v>3.146822481682356</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.207167949394524</v>
+        <v>3.205981162949868</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.71750605369057</v>
+        <v>1.717352663686249</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.855030467351931</v>
+        <v>3.854535974973928</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.586813906956962</v>
+        <v>2.635359826722734</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.614114943891323</v>
+        <v>3.638072352840936</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.624295095574062</v>
+        <v>4.672306774564383</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.52218995543695</v>
+        <v>4.571437517830667</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.643689550739005</v>
+        <v>4.716946660518701</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.428807250759505</v>
+        <v>3.528154576054078</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.048923610747487</v>
+        <v>5.148831646766162</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.353374755803543</v>
+        <v>4.477071376831788</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.568260398840494</v>
+        <v>3.716949946618321</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.151660282643675</v>
+        <v>2.323659042210338</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.742964566480573</v>
+        <v>2.713768772127942</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.082422866913298</v>
+        <v>3.082269476908976</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.771283404957963</v>
+        <v>5.77078891257996</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.166895770838806</v>
+        <v>4.215441690604578</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.530367881497355</v>
+        <v>5.554325290446968</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.085316370845256</v>
+        <v>6.133328049835576</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.684345808081972</v>
+        <v>6.733593370475688</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.623363651559195</v>
+        <v>6.696620761338892</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.920566390410571</v>
+        <v>5.019913715705144</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>5.995182929378522</v>
+        <v>6.095090965397198</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.963463000710391</v>
+        <v>5.087159621738635</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.756531763601679</v>
+        <v>4.905221311379506</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.850071251781294</v>
+        <v>3.022070011347957</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>403</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.60593260470138</v>
+        <v>2.576736810348748</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.483580258535817</v>
+        <v>2.482393472091161</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.585086789413523</v>
+        <v>2.584933399409202</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.700423595532911</v>
+        <v>4.699929103154908</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.169578211171711</v>
+        <v>3.218124130937483</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.211369114255923</v>
+        <v>4.235326523205536</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.615492501888021</v>
+        <v>5.663504180878341</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.900284900284902</v>
+        <v>4.949532462678619</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.839302743762126</v>
+        <v>4.912559853541822</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.99682811616676</v>
+        <v>3.096175441461334</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.784682789172074</v>
+        <v>3.884590825190749</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.826505110261891</v>
+        <v>2.950201731290136</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.150771130397608</v>
+        <v>3.299460678175436</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.143256160276749</v>
+        <v>1.315254919843412</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>347</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.850496073212049</v>
+        <v>2.821300278859418</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.968416608390292</v>
+        <v>2.967229821945637</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.726382975796632</v>
+        <v>3.726229585792311</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.585714747627073</v>
+        <v>5.58522025524907</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.3183185662893</v>
+        <v>3.366864486055071</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.480245910045433</v>
+        <v>4.504203318995046</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.97190442685995</v>
+        <v>5.019916105850271</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.504835783073212</v>
+        <v>4.554083345466928</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.308406940671468</v>
+        <v>5.381664050451164</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.305750392180229</v>
+        <v>3.405097717474803</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.67741811000073</v>
+        <v>3.777326146019405</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.847242948235021</v>
+        <v>2.970939569263265</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.003460971002298</v>
+        <v>3.152150518780125</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.9237211169060586</v>
+        <v>1.095719876472721</v>
       </c>
     </row>
     <row r="29">
@@ -3413,98 +3413,98 @@
         <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.336359716973959</v>
+        <v>2.307163922621328</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.054077278395177</v>
+        <v>2.052890491950521</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.779564259819857</v>
+        <v>4.779069767441854</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.244596965860381</v>
+        <v>3.293142885626153</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.538648736359249</v>
+        <v>4.562606145308862</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.453938377093081</v>
+        <v>4.501950056083402</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.986869733306342</v>
+        <v>4.036117295700059</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.587017144889877</v>
+        <v>5.660274254669574</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.740420607696237</v>
+        <v>3.83976793299081</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.532397190299825</v>
+        <v>4.632305226318501</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.237871688170102</v>
+        <v>3.361568309198347</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.153269007614163</v>
+        <v>2.301958555391991</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.05010100335565</v>
+        <v>1.222099762922312</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 2.884</t>
+          <t>X &gt; 2.883</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>249</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.137557865047981</v>
+        <v>2.10836207069535</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.739223177606632</v>
+        <v>3.738036391161977</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.549271069960035</v>
+        <v>4.549117679955714</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.081102639251199</v>
+        <v>5.080608146873196</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.329961680533025</v>
+        <v>1.378507600298796</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.832154987276546</v>
+        <v>2.856112396226159</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.345838202307561</v>
+        <v>2.393849881297882</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>3.083588835629257</v>
+        <v>3.132836398022974</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.825819530512106</v>
+        <v>3.899076640291803</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.574294308479431</v>
+        <v>2.673641633774004</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.771199575922054</v>
+        <v>2.871107611940729</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.002364876871752</v>
+        <v>2.126061497899997</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.180607597855527</v>
+        <v>1.329297145633355</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6016888804319933</v>
+        <v>-0.429690120865331</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>208</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.807545507927188</v>
+        <v>2.778349713574556</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.080974799478746</v>
+        <v>4.07978801303409</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.166972645492933</v>
+        <v>4.166819255488612</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.816428558312069</v>
+        <v>3.815934065934066</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.835831312908674</v>
+        <v>1.884377232674446</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.094743804082221</v>
+        <v>3.118701213031834</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.010033444816052</v>
+        <v>3.058045123806373</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.985272493337014</v>
+        <v>4.034520055730731</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.924290336814238</v>
+        <v>3.997547446593934</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.074371540484378</v>
+        <v>3.173718865778952</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.831208843762646</v>
+        <v>3.931116879781321</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.904048534579509</v>
+        <v>3.027745155607754</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.003128450496867</v>
+        <v>2.151817998274694</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.267325639184932</v>
+        <v>1.439324398751594</v>
       </c>
     </row>
     <row r="32">
@@ -3566,101 +3566,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6619411123227934</v>
+        <v>0.3307972660221097</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.479326447830388</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.227412205932495</v>
+        <v>2.899336738006092</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>3.029220779220772</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03779506071769134</v>
+        <v>0.2672443655415861</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3965599617773492</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.422085680150197</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.249295698342181</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.654041870154707</v>
+        <v>1.993648935709025</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.020769283323084</v>
+        <v>2.357690306354748</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.279493407356</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.07928913192071718</v>
+        <v>0.3161536626103612</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9964106245513236</v>
+        <v>-0.571165111737912</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 3.146</t>
+          <t>X &gt; 3.145</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.001353473011747042</v>
+        <v>-0.3974357685489593</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.93626667072806</v>
+        <v>1.540513906858578</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.8322754278169953</v>
+        <v>1.146775918543874</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.9625005714053572</v>
+        <v>0.5724346076458744</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2850088398463697</v>
+        <v>-0.6210398854187176</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7215850479447496</v>
+        <v>0.355970985512883</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.909224602101567</v>
+        <v>-3.225811864275961</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5394138132641899</v>
+        <v>-0.8747432162085929</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.437275402411082</v>
+        <v>-3.728617233796101</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.577974340584909</v>
+        <v>-3.848220462498411</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.364235782533044</v>
+        <v>-2.643910205809149</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.039077488333753</v>
+        <v>-3.289968820556929</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.87766805795922</v>
+        <v>-5.093577451346107</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.361152265888713</v>
+        <v>-5.548757941443419</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>114</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.782241864202497</v>
+        <v>2.753046069849866</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.5833301937736195</v>
+        <v>-0.5845169802182753</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.855294560984802</v>
+        <v>-1.855447950989124</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.60226239985257</v>
+        <v>-2.602756892230573</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.720370905769322</v>
+        <v>-3.696413496819709</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.313853194860059</v>
+        <v>-7.265841515869738</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-6.903728856190654</v>
+        <v>-6.854481293796937</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.841903995169574</v>
+        <v>-7.768646885389877</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.937436826587152</v>
+        <v>-6.838089501292579</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-5.353373867579734</v>
+        <v>-5.229677246551489</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-7.527910685805431</v>
+        <v>-7.379221138027603</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-9.056561000491179</v>
+        <v>-8.884562240924517</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>3.960476410407132</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.200828737015989</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>-0.3693798395340124</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>0.9369747899159648</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.275890298812939</v>
+        <v>-6.611097880447723</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-6.978516269177852</v>
+        <v>-6.338312361628795</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.63465519987259</v>
+        <v>-9.928380215560132</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.720771462706942</v>
+        <v>-8.041271799472895</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-8.781753619229718</v>
+        <v>-8.078244408609692</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-12.01262479651196</v>
+        <v>-11.25501416589525</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.02684976429596</v>
+        <v>-10.28268402519605</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-10.99247161194064</v>
+        <v>-10.22451728783116</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-12.60309865573024</v>
+        <v>-12.97261639086557</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-13.5678391959799</v>
+        <v>-13.9000421170855</v>
       </c>
     </row>
   </sheetData>
@@ -3904,157 +3904,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.7866</t>
+          <t>X &lt; 0.7868</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>3.960476410407132</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.3840883525923</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.37026934878964</v>
+        <v>12.57179663105421</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.07192306380657</v>
+        <v>16.23109243697479</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22.48601446309183</v>
+        <v>21.62419623719934</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20.40243611177453</v>
+        <v>19.54404057954768</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>23.88915432393694</v>
+        <v>23.01279625502811</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>24.6125618706264</v>
+        <v>23.72343408288005</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>24.55157971410362</v>
+        <v>23.68646147374326</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30.8445180606309</v>
+        <v>29.92145642234003</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>34.21124547379928</v>
+        <v>33.24672773950984</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>33.05514743567841</v>
+        <v>33.30489447687473</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>32.63499658236501</v>
+        <v>31.7332659620756</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>35.2416846135439</v>
+        <v>34.33525200056156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.874</t>
+          <t>X &lt; 0.8741</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>347</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8332050069296244</v>
+        <v>0.8040092125769931</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.968416608390292</v>
+        <v>2.967229821945637</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.132723033433521</v>
+        <v>1.1325696434292</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.415685929183262</v>
+        <v>2.415191436805259</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.471056318450685</v>
+        <v>4.519602238216457</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.90387703396474</v>
+        <v>3.927834442914353</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.412826617061675</v>
+        <v>6.460838296051996</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.522126849355637</v>
+        <v>6.571374411749353</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.88477581675216</v>
+        <v>5.958032926531857</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.475779210624033</v>
+        <v>6.575126535918606</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.847446928444533</v>
+        <v>6.947354964463209</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.017271766678824</v>
+        <v>6.140968387707069</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>5.885305351405755</v>
+        <v>6.033994899183583</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.263778753793666</v>
+        <v>7.435777513360328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.9613</t>
+          <t>X &lt; 0.9615</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>548</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.07382849501309607</v>
+        <v>0.04463270066046476</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.382350431146342</v>
+        <v>1.381163644701687</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2576520390920365</v>
+        <v>0.2574986490877151</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.482767693629306</v>
+        <v>1.482273201251303</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.586813906956962</v>
+        <v>2.635359826722734</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.519224432942423</v>
+        <v>2.543181841892036</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.076849840099605</v>
+        <v>4.124861519089926</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.069635210911407</v>
+        <v>5.118882773305124</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.278726047089364</v>
+        <v>4.351983156869061</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.253624769007679</v>
+        <v>5.352972094302253</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.596368866221944</v>
+        <v>5.696276902240619</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.718338259453169</v>
+        <v>4.842034880481414</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.933223902490134</v>
+        <v>4.081913450267962</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.70640480819111</v>
+        <v>4.878403567757772</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>635</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5124120935264855</v>
+        <v>-0.5416078878791168</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.0811262228585079</v>
+        <v>0.07993943641385215</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.416007366620931</v>
+        <v>-1.416160756625253</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.02593970334753237</v>
+        <v>-0.0264341957255354</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.380652633320544</v>
+        <v>0.4291985530863158</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3630660330343716</v>
+        <v>0.3870234419839846</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.538198193453248</v>
+        <v>1.586209872443568</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.016011439430287</v>
+        <v>2.065259001824003</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.95502928290751</v>
+        <v>2.028286392687207</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.994874266105207</v>
+        <v>3.09422159139978</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.262614052726903</v>
+        <v>3.362522088745578</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.352110315318455</v>
+        <v>2.4758069363467</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.61699883208378</v>
+        <v>1.765688379861608</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.630136057113461</v>
+        <v>2.802134816680123</v>
       </c>
     </row>
     <row r="10">
@@ -4119,98 +4119,98 @@
         <v>703</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.414059700520134</v>
+        <v>-1.383351261506704</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3225430908812541</v>
+        <v>-0.2904720086343886</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.428552028979105</v>
+        <v>-1.247590278639237</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.160346800042241</v>
+        <v>0.1498993963782738</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.7238387535477031</v>
+        <v>0.8658788058544431</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8789652725142219</v>
+        <v>1.217353972701545</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.358977530602246</v>
+        <v>2.65003729005597</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.887641461495448</v>
+        <v>3.115202121540271</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.968906815641247</v>
+        <v>3.160804402404075</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.11045316867127</v>
+        <v>4.266376208436292</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.332494542416761</v>
+        <v>4.432402578435436</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.371140120092143</v>
+        <v>3.494836741120388</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.239751713435922</v>
+        <v>2.38844126121375</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.318972427673835</v>
+        <v>3.490971187240497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 1.223</t>
+          <t>X &lt; 1.224</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2027385725007846</v>
+        <v>-0.08407632192840708</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.370082750351401</v>
+        <v>1.356948056781803</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4410111070313931</v>
+        <v>0.4358675263162439</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.239019505271244</v>
+        <v>1.224804886325067</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.852050033946675</v>
+        <v>1.633988501310689</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.976621877757644</v>
+        <v>1.854964949295578</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.288740245261991</v>
+        <v>3.053460911832417</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.980040421901798</v>
+        <v>3.73045359712966</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.523653186781679</v>
+        <v>4.241665634260507</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.850276107501394</v>
+        <v>5.522357069680318</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.250169870643873</v>
+        <v>5.990651656381964</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.754905304927803</v>
+        <v>5.403921137898834</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.773524720893143</v>
+        <v>5.322701736385326</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.560454840081128</v>
+        <v>6.006632091059295</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3257436167412493</v>
+        <v>-0.2916817907572877</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.6965087478427208</v>
+        <v>0.6462499456360646</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5217620702305439</v>
+        <v>0.4702380589074195</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.304544375079566</v>
+        <v>1.245936698032502</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.938972116741525</v>
+        <v>1.746073755329881</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.631873341211765</v>
+        <v>2.495802261084044</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.683410327898315</v>
+        <v>2.484090776267124</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.393588591809227</v>
+        <v>3.183166473690449</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.077869396643294</v>
+        <v>3.79763996575862</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.408913410430245</v>
+        <v>4.056300385720746</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.03940282369576</v>
+        <v>4.678336527603378</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.127135499833571</v>
+        <v>4.702776627150847</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.195972192121097</v>
+        <v>4.704868396152676</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.173099899797904</v>
+        <v>5.610692288842522</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1385</v>
+        <v>1396</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7641778331094571</v>
+        <v>-0.7003176446172859</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5249343832021083</v>
+        <v>0.5231883626844365</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.09765371227715747</v>
+        <v>0.09719485004330863</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7687996639089789</v>
+        <v>0.7637675269254203</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.059151034793679</v>
+        <v>0.9543197456774664</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.899205673870725</v>
+        <v>1.836649930980556</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.214277476646302</v>
+        <v>2.101304074406741</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.866473068462817</v>
+        <v>2.745839050573267</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.566653369465044</v>
+        <v>3.392553760765132</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.766969978763157</v>
+        <v>3.539103481163565</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.253786986081415</v>
+        <v>4.020810067222904</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.331797966114081</v>
+        <v>4.050497439089654</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.316093263461681</v>
+        <v>3.984729181579581</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.019061268176884</v>
+        <v>4.635268855441041</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1643</v>
+        <v>1654</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8504812479256643</v>
+        <v>-0.8004537565006657</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4969359604561845</v>
+        <v>-0.4918483338123423</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9802229642177949</v>
+        <v>-0.9735133848440327</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5756441300401178</v>
+        <v>-0.5710851648351749</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4760517193133396</v>
+        <v>-0.5469331887141422</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4599769960870717</v>
+        <v>0.4203766735520631</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4086348434174596</v>
+        <v>0.3326248487172307</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7026886429848176</v>
+        <v>0.6227962373804061</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.282393398800792</v>
+        <v>1.1619073482956</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.863253423628549</v>
+        <v>1.698934602997106</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.754496066867617</v>
+        <v>1.58994191111691</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.702563849052261</v>
+        <v>1.501825423166281</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.621788379375772</v>
+        <v>1.383168219050901</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.126448257285041</v>
+        <v>1.84858865323956</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1817</v>
+        <v>1828</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5137029157802573</v>
+        <v>-0.4731753773041447</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1281874161077496</v>
+        <v>-0.1258976056950161</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7122564405195249</v>
+        <v>-0.7077990571394821</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4978634714972046</v>
+        <v>-0.4942484066531989</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.185189834618491</v>
+        <v>-0.2465008712575525</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3613402213635837</v>
+        <v>0.3283543050378768</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1422871560171401</v>
+        <v>0.07963388926435044</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5829664888642441</v>
+        <v>0.5160442567205834</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9367660608706387</v>
+        <v>0.8367454826004774</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.215978011992</v>
+        <v>1.080588197320772</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9328571954109961</v>
+        <v>0.7983710074122925</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7787789443566382</v>
+        <v>0.6144412464022082</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8300303714582</v>
+        <v>0.6330183179113149</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.417615635374766</v>
+        <v>1.186841651739314</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2077</v>
+        <v>2088</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8062748822089887</v>
+        <v>-0.7728438572525249</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1428441054076544</v>
+        <v>-0.1409079576618879</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.751241324445175</v>
+        <v>-0.7471507668663619</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4036057198199643</v>
+        <v>-0.4009941440828015</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4845831719353342</v>
+        <v>-0.5307029184572087</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3049979409832559</v>
+        <v>-0.3274232731689821</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.315671560351511</v>
+        <v>-0.3621861961862791</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08453252161923075</v>
+        <v>-0.1335241732017494</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2171485352920328</v>
+        <v>0.142435167568614</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4991026239132026</v>
+        <v>0.3966560624255138</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5139011514549523</v>
+        <v>0.4107640857556447</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.2869896675206434</v>
+        <v>0.1610723547244248</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3271456267758381</v>
+        <v>0.1758081297325162</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.109924061465591</v>
+        <v>0.9309247524209283</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2281</v>
+        <v>2292</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.6936448884245081</v>
+        <v>-0.6662940374683259</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1889185213304145</v>
+        <v>-0.1870389100428369</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6038019551245952</v>
+        <v>-0.6007915531556236</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.188162987200478</v>
+        <v>-0.1868561499317352</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3534532017033456</v>
+        <v>-0.3918070350352423</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1633131236994743</v>
+        <v>-0.1823021314497666</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2242322894496738</v>
+        <v>-0.2627967137818672</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2070191550705545</v>
+        <v>0.1653528869552048</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3889750396879208</v>
+        <v>0.3265802988091977</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.8762988254532331</v>
+        <v>0.789974561302941</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7840917751919818</v>
+        <v>0.6977081316666869</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4492404210985939</v>
+        <v>0.3447426742181818</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.3667027646204346</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.137490546614202</v>
+        <v>0.9895996034770675</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2491</v>
+        <v>2502</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4841109187132631</v>
+        <v>-0.4623981071931524</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.03696828420545017</v>
+        <v>-0.03600967376598874</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4900709503995841</v>
+        <v>-0.4878227598776377</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2982717154245904</v>
+        <v>-0.2966333030027357</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3349379178605574</v>
+        <v>-0.3661052597435202</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2958431999501556</v>
+        <v>-0.3106582721045399</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.318783454857531</v>
+        <v>-0.3496870404024719</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1233116537933867</v>
+        <v>-0.1559167004955029</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1582646957885956</v>
+        <v>0.1082451852334358</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4127020476525587</v>
+        <v>0.3439717972050644</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2306444122038229</v>
+        <v>0.1623083430087107</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.2337758351943293</v>
+        <v>-0.3161354047264808</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1900435460459136</v>
+        <v>-0.2894832095067343</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4598031736937855</v>
+        <v>0.3417409270674128</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2722</v>
+        <v>2733</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4151025021979748</v>
+        <v>-0.3979486784922344</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.004459690593478172</v>
+        <v>0.005071745694870344</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2973381991691753</v>
+        <v>-0.2960647992321768</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.476706929918592</v>
+        <v>-0.4745325764283095</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.06661462699481291</v>
+        <v>0.04055183852082678</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.165329455991035</v>
+        <v>-0.1774007149562564</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.156807043387559</v>
+        <v>-0.1817078239757635</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1292494840881915</v>
+        <v>0.1025333677199498</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6019228436546626</v>
+        <v>0.5605215433518111</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8363078800069275</v>
+        <v>0.7800607336297745</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5423944471500803</v>
+        <v>0.4870098172532025</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2672305067923162</v>
+        <v>0.2002595698954792</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.4109199058769732</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.7388680570903219</v>
+        <v>0.6441992896857656</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2907</v>
+        <v>2918</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3918749346439441</v>
+        <v>-0.377733796910185</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.00176563933433016</v>
+        <v>0.00227422988891135</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1003073671606245</v>
+        <v>-0.09986404414108563</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2256919026462398</v>
+        <v>-0.2246291959406719</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1462143455139326</v>
+        <v>0.1245680292369613</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.08641466009510168</v>
+        <v>-0.09650463375295004</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.2896867389123656</v>
+        <v>-0.3094762437149896</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1201633512852354</v>
+        <v>-0.1411350005672816</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1468178093417123</v>
+        <v>0.1143860476097487</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3808416934849319</v>
+        <v>0.3361602915673956</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1268075749283852</v>
+        <v>0.08282335543506747</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2319418930059669</v>
+        <v>-0.2849524207884571</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2545691476408933</v>
+        <v>-0.3184036266231871</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1126325519187574</v>
+        <v>-0.1871848014381996</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3061</v>
+        <v>3072</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2688145341127495</v>
+        <v>-0.2572755201868162</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1383110399665526</v>
+        <v>-0.1373874833242894</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2551026750198844</v>
+        <v>-0.2541368561908186</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7259091918570064</v>
+        <v>-0.7231389635672656</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3672506214436169</v>
+        <v>-0.3835552567770222</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5408678960456044</v>
+        <v>-0.54763245330183</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7057423048579992</v>
+        <v>-0.7206542541135263</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6009242411316507</v>
+        <v>-0.6166645296643765</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2853413556941717</v>
+        <v>-0.3109385912551232</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.008041560281093041</v>
+        <v>-0.04412148632667368</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1944489188402869</v>
+        <v>-0.2300776167790346</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3050036766764279</v>
+        <v>-0.348900157439644</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3476478143878197</v>
+        <v>-0.4004987055226437</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1035184791273309</v>
+        <v>-0.1657437102227561</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3214</v>
+        <v>3225</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4201785034193861</v>
+        <v>-0.4100500583644404</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2173346096490221</v>
+        <v>-0.2162422619118516</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1922998649423704</v>
+        <v>-0.1916004459471665</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7276161067003457</v>
+        <v>-0.7249944800176706</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2564023919530101</v>
+        <v>-0.2700159931473465</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3455465077164632</v>
+        <v>-0.3515217282705905</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5065524219716053</v>
+        <v>-0.5191635586003258</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4599018974895515</v>
+        <v>-0.4730448801071887</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.2553700928461922</v>
+        <v>-0.276386823470375</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.06272986029011207</v>
+        <v>-0.09220652193337031</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.281109130460834</v>
+        <v>-0.3100183790119289</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2604175963045421</v>
+        <v>-0.2965200585706924</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1965963969729287</v>
+        <v>-0.240403853029612</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.1710928185241229</v>
+        <v>-0.2219755416181002</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3402</v>
+        <v>3413</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2115163233601152</v>
+        <v>-0.2042157361537633</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1377963239496722</v>
+        <v>-0.1370845304807915</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.03993575036344765</v>
+        <v>0.03984226052095607</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4000246836394226</v>
+        <v>-0.3986269354367522</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1602560063976384</v>
+        <v>-0.1707637105436461</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2573879351462836</v>
+        <v>-0.2620016853559406</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3848263155467819</v>
+        <v>-0.3944964866299685</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3077935955037248</v>
+        <v>-0.317995299636344</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1472196765067508</v>
+        <v>-0.1633991258505887</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.04662638487662463</v>
+        <v>0.02388545365406003</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1122284091459775</v>
+        <v>-0.134592001501332</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.03197695579380877</v>
+        <v>-0.06001810602081292</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.0535975152799395</v>
+        <v>-0.08726541391943243</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.07119666527817969</v>
+        <v>0.03181014330297671</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3542</v>
+        <v>3553</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3852760867931408</v>
+        <v>-0.3788723408712826</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3217025737951431</v>
+        <v>-0.3204978861999237</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.08214510981677137</v>
+        <v>-0.08186415986146756</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4715132296297284</v>
+        <v>-0.469969127140061</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.09347354162850507</v>
+        <v>-0.1018664506495242</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3440427614649053</v>
+        <v>-0.3472655638026723</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4134661325296705</v>
+        <v>-0.4207794224338954</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3579110987191854</v>
+        <v>-0.3656193524867888</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3188674780238685</v>
+        <v>-0.3309971117145309</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.05347565462170678</v>
+        <v>-0.07110174796210345</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4398392195985394</v>
+        <v>-0.4563755490496888</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3332756536476111</v>
+        <v>-0.3544089069260608</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2860549881361862</v>
+        <v>-0.3118199394769192</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1855692919708574</v>
+        <v>-0.2158315907697101</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3631</v>
+        <v>3642</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4776229460118486</v>
+        <v>-0.4718081313165285</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4824397574164578</v>
+        <v>-0.4808094354944004</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2584275995119256</v>
+        <v>-0.2576264056118589</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.580213319447644</v>
+        <v>-0.57839148803005</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3894434123660488</v>
+        <v>-0.3955566105297237</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5442525389536854</v>
+        <v>-0.5462092190018808</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6965678153860821</v>
+        <v>-0.7016782988383952</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6813747856968533</v>
+        <v>-0.686718135902197</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6998740026966388</v>
+        <v>-0.7087707074209533</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5169150958504005</v>
+        <v>-0.5302876323855301</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7613676771297762</v>
+        <v>-0.7740904643149094</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.6566609871126801</v>
+        <v>-0.6732807668781007</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.5383829015871768</v>
+        <v>-0.5591239557361618</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3247341875209955</v>
+        <v>-0.3496334857581829</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3710</v>
+        <v>3721</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3455413327100203</v>
+        <v>-0.340856334795923</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3844180827599288</v>
+        <v>-0.3831362178381781</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3885128526155128</v>
+        <v>-0.3873484417659014</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7276161067003457</v>
+        <v>-0.725408737603864</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5254837635179825</v>
+        <v>-0.5300381106953225</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6976176805869514</v>
+        <v>-0.6985729582246307</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.7678271127055183</v>
+        <v>-0.7716016242953074</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.8436378320749256</v>
+        <v>-0.8473451276504207</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8361662321887664</v>
+        <v>-0.8429187163360012</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6213639302914871</v>
+        <v>-0.6320374584337571</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.7572692684833129</v>
+        <v>-0.7676148396270932</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6271185741738137</v>
+        <v>-0.6408482037591838</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6011353805252568</v>
+        <v>-0.6180947864150923</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3602920261685725</v>
+        <v>-0.3809058950073094</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3776</v>
+        <v>3787</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.277168339850796</v>
+        <v>-0.2732697196238263</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2642246156784367</v>
+        <v>-0.2633336586608905</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2750963760585279</v>
+        <v>-0.2742833491210988</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5003356336502307</v>
+        <v>-0.4988336656759174</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3374742454695365</v>
+        <v>-0.341650164585829</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4485152624326503</v>
+        <v>-0.4497593119504302</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5982139778643543</v>
+        <v>-0.601579384526616</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5221615057680609</v>
+        <v>-0.5258796684575486</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5157997899328635</v>
+        <v>-0.5220890350678715</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3195031033902609</v>
+        <v>-0.3291370886069487</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4036060238254464</v>
+        <v>-0.4130580745519481</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3015038537415435</v>
+        <v>-0.3137849822406693</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3361823578369822</v>
+        <v>-0.3510249876728295</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.1220159514278336</v>
+        <v>-0.1399650733289945</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3832</v>
+        <v>3843</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2572489304043089</v>
+        <v>-0.253887758496937</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.267960604347401</v>
+        <v>-0.2670891694462085</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.3364701776220187</v>
+        <v>-0.3354960213466427</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5044880316050424</v>
+        <v>-0.5030032256868537</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2997804067957262</v>
+        <v>-0.3032975017292543</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4048555548921371</v>
+        <v>-0.4058578425581132</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.449401103443698</v>
+        <v>-0.4524443866831263</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4072897385946845</v>
+        <v>-0.4105655808981723</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.48006703372765</v>
+        <v>-0.4853007862542995</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2990342508046311</v>
+        <v>-0.3071403451946324</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3327416125606959</v>
+        <v>-0.3408039970537473</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2576925673024348</v>
+        <v>-0.2681186035199872</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2719021541711015</v>
+        <v>-0.2845463657691667</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.0836459362125197</v>
+        <v>-0.09893697557534864</v>
       </c>
     </row>
     <row r="29">
@@ -5104,101 +5104,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3878</v>
+        <v>3889</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1807361281956261</v>
+        <v>-0.1779744594333721</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1589401698706752</v>
+        <v>-0.1584004199120983</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2055672599603184</v>
+        <v>-0.2049756163062639</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.3700228503615577</v>
+        <v>-0.3689407540395067</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2512538427383504</v>
+        <v>-0.2542934860373194</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3515525655285998</v>
+        <v>-0.3524106876412603</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3450799102972937</v>
+        <v>-0.3478149298976163</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.3089721394761042</v>
+        <v>-0.3119053417216264</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4330909504537317</v>
+        <v>-0.4375301876362485</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.290022308839923</v>
+        <v>-0.2968841890136815</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3515206272301654</v>
+        <v>-0.3582538214598827</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.2511854067369086</v>
+        <v>-0.2600442202695206</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.1670879018540603</v>
+        <v>-0.1781207005586012</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.08150603455648309</v>
+        <v>-0.09458781914107561</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 2.884</t>
+          <t>X &lt; 2.883</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3930</v>
+        <v>3941</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1349865352262114</v>
+        <v>-0.1327724217509143</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2361914183724068</v>
+        <v>-0.23545941345796</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.287431742303994</v>
+        <v>-0.2866220400579422</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3211153698409959</v>
+        <v>-0.3201901869327912</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0840722159057421</v>
+        <v>-0.08689832720870783</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1790773468338998</v>
+        <v>-0.1800891331122614</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.1483651796735046</v>
+        <v>-0.1509798937292786</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.195074598595447</v>
+        <v>-0.1976377661788007</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2420912485635398</v>
+        <v>-0.2460390480062458</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1629383026973557</v>
+        <v>-0.1687545669986648</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1754458922971267</v>
+        <v>-0.1812641468999061</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.1268028622434016</v>
+        <v>-0.1342605409528588</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.07478282672756364</v>
+        <v>-0.08396625805750801</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.03812227257699163</v>
+        <v>0.02714865265045319</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3971</v>
+        <v>3982</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1465786811367664</v>
+        <v>-0.1446550038607057</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2131164344191632</v>
+        <v>-0.2124676781950612</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2176620568213252</v>
+        <v>-0.2170544465669053</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.1994014418811645</v>
+        <v>-0.1988262238763241</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.09594294298618422</v>
+        <v>-0.09820858541625199</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.161776001821849</v>
+        <v>-0.1625789103535453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1573873696635815</v>
+        <v>-0.1594568527830944</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.2084326574337609</v>
+        <v>-0.2104263218636007</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2052948667146239</v>
+        <v>-0.2085502555534262</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.160872774948615</v>
+        <v>-0.1656130266136557</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2005262807002097</v>
+        <v>-0.2051875309898463</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1520367720091969</v>
+        <v>-0.1580750482847435</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1048969581327768</v>
+        <v>-0.1123721174092651</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.06638220421820051</v>
+        <v>-0.07518319310405985</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4004</v>
+        <v>4014</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02883736486345612</v>
+        <v>-0.01445749163642063</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1080383785782644</v>
+        <v>-0.09428245201998919</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1406717648912021</v>
+        <v>-0.1267784511525676</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1214714838480688</v>
+        <v>-0.1324907696677187</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.00164817733008249</v>
+        <v>-0.01169152581041288</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06117306070802186</v>
+        <v>-0.07335784675472468</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01730191805311421</v>
+        <v>0.003887145500179656</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.0620610957671488</v>
+        <v>-0.05034408510356059</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08435847259536189</v>
+        <v>-0.09850113035785313</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.07221989203519996</v>
+        <v>-0.08732757906540201</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08825421127565392</v>
+        <v>-0.1032993512368492</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.0398529209295404</v>
+        <v>-0.05607341625862716</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.003464568810514379</v>
+        <v>-0.01385879068976692</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.04354941540871238</v>
+        <v>0.0250436122734996</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 3.146</t>
+          <t>X &lt; 3.145</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4038</v>
+        <v>4048</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.710928034512563e-05</v>
+        <v>0.01389703992463609</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.06741076557349146</v>
+        <v>-0.05388004304776217</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.02898267110946051</v>
+        <v>-0.0401187929128497</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03352583512059226</v>
+        <v>-0.02003097937055998</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.009929885450546294</v>
+        <v>0.02173716138266002</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.02514668605048342</v>
+        <v>-0.01246249505494745</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1014093124589266</v>
+        <v>0.1129630788476419</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.01880745491352087</v>
+        <v>0.0306397475830309</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.1198752984763658</v>
+        <v>0.1306349980752657</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1248130583924905</v>
+        <v>0.13485866378943</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.0824937503927643</v>
+        <v>0.09267717828311817</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1060668133304503</v>
+        <v>0.1153519932145812</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1702775925160296</v>
+        <v>0.1786337362536869</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1872021965057726</v>
+        <v>0.1946451649419316</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.07777723700811379</v>
+        <v>-0.07675403569646733</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01631092521221689</v>
+        <v>0.0163001310530575</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.05188998526798372</v>
+        <v>0.05175460396689857</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.07279948799587999</v>
+        <v>0.07261729948953644</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1369717532243797</v>
+        <v>0.1352481487840507</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.104130194760053</v>
+        <v>0.1031809839954505</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2047591513295828</v>
+        <v>0.2028669930955544</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1933247579478561</v>
+        <v>0.1914284339766823</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2196503821742795</v>
+        <v>0.2170119443603156</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1943641676655048</v>
+        <v>0.1910642654772943</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1755663053767478</v>
+        <v>0.1723006163683394</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1500576889363359</v>
+        <v>0.1461949990453348</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2110629164244529</v>
+        <v>0.2063358375607436</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2539847365451422</v>
+        <v>0.2484887378472393</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4095</v>
+        <v>4105</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.09532693608449705</v>
+        <v>-0.08174854173982027</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.02479243202486714</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.005626552678599239</v>
+        <v>0.00762810650154222</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03265323687205068</v>
+        <v>-0.01935427877104701</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1489217312622557</v>
+        <v>0.1365929314142136</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1428699406802139</v>
+        <v>0.1309887067197693</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2177745092124113</v>
+        <v>0.2052315949228145</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1786258968220977</v>
+        <v>0.1662632213464335</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1799188546378829</v>
+        <v>0.1670683150199039</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2461723549419332</v>
+        <v>0.2328245811879057</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2260262030748805</v>
+        <v>0.2127624494015734</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.225376523164023</v>
+        <v>0.211610413797338</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.2584619841507134</v>
+        <v>0.2685514839804171</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2783146501739466</v>
+        <v>0.2878206041296636</v>
       </c>
     </row>
   </sheetData>
